--- a/交接班容量报表空模板.xlsx
+++ b/交接班容量报表空模板.xlsx
@@ -69,10 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="796" uniqueCount="494">
-  <si>
-    <t>世纪互联南通数据中心E栋FM运维交接班重要事项</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="784" uniqueCount="491">
   <si>
     <t>班次</t>
   </si>
@@ -122,46 +119,46 @@
     <t>/</t>
   </si>
   <si>
+    <t>二、【交接班组】</t>
+  </si>
+  <si>
+    <t>FM运维值班团队</t>
+  </si>
+  <si>
+    <t>交班:</t>
+  </si>
+  <si>
+    <t>接班：</t>
+  </si>
+  <si>
+    <t>晨会到场工程师</t>
+  </si>
+  <si>
+    <t>应急人员（15min）</t>
+  </si>
+  <si>
+    <t>三、【监控中心当前运营状态】</t>
+  </si>
+  <si>
+    <t>接班未恢复告警：0</t>
+  </si>
+  <si>
+    <t>告警总数</t>
+  </si>
+  <si>
+    <t>变化率：</t>
+  </si>
+  <si>
+    <t>告警原因：</t>
+  </si>
+  <si>
+    <t>交班未恢复告警：0</t>
+  </si>
+  <si>
+    <t>四、【电气】</t>
+  </si>
+  <si>
     <t>E楼</t>
-  </si>
-  <si>
-    <t>二、【交接班组】</t>
-  </si>
-  <si>
-    <t>FM运维值班团队</t>
-  </si>
-  <si>
-    <t>交班:</t>
-  </si>
-  <si>
-    <t>接班：</t>
-  </si>
-  <si>
-    <t>晨会到场工程师</t>
-  </si>
-  <si>
-    <t>应急人员（15min）</t>
-  </si>
-  <si>
-    <t>三、【监控中心当前运营状态】</t>
-  </si>
-  <si>
-    <t>接班未恢复告警：0</t>
-  </si>
-  <si>
-    <t>告警总数</t>
-  </si>
-  <si>
-    <t>变化率：</t>
-  </si>
-  <si>
-    <t>告警原因：</t>
-  </si>
-  <si>
-    <t>交班未恢复告警：0</t>
-  </si>
-  <si>
-    <t>四、【电气】</t>
   </si>
   <si>
     <t>线路名称</t>
@@ -509,9 +506,6 @@
     <t>110KV变电站</t>
   </si>
   <si>
-    <t>E楼能耗一览</t>
-  </si>
-  <si>
     <t>机柜总数</t>
   </si>
   <si>
@@ -586,9 +580,6 @@
   </si>
   <si>
     <t>4#主变</t>
-  </si>
-  <si>
-    <t>E楼容量一览表</t>
   </si>
   <si>
     <t>配电间</t>
@@ -3559,20 +3550,28 @@
   <cols>
     <col min="2" max="2" width="11.7727272727273" style="1" customWidth="1"/>
     <col min="3" max="3" width="9" style="1" customWidth="1"/>
-    <col min="5" max="8" width="9" style="1" customWidth="1"/>
+    <col min="5" max="5" width="9" style="1" customWidth="1"/>
+    <col min="6" max="6" width="11.9363636363636" style="1" customWidth="1"/>
+    <col min="7" max="8" width="9" style="1" customWidth="1"/>
     <col min="9" max="9" width="16.4090909090909" style="1" customWidth="1"/>
-    <col min="10" max="13" width="9" style="1" customWidth="1"/>
+    <col min="10" max="11" width="9" style="1" customWidth="1"/>
+    <col min="12" max="12" width="11.9363636363636" style="1" customWidth="1"/>
+    <col min="13" max="13" width="9" style="1" customWidth="1"/>
     <col min="14" max="14" width="8.74545454545455" style="1" customWidth="1"/>
     <col min="15" max="15" width="17.1090909090909" style="1" customWidth="1"/>
-    <col min="16" max="27" width="9" style="1" customWidth="1"/>
+    <col min="16" max="18" width="9" style="1" customWidth="1"/>
+    <col min="19" max="19" width="12.5909090909091" style="1" customWidth="1"/>
+    <col min="20" max="21" width="9" style="1" customWidth="1"/>
+    <col min="22" max="22" width="14.1545454545455" style="1" customWidth="1"/>
+    <col min="23" max="24" width="9" style="1" customWidth="1"/>
+    <col min="25" max="25" width="10.2545454545455" style="1" customWidth="1"/>
+    <col min="26" max="27" width="9" style="1" customWidth="1"/>
     <col min="28" max="28" width="12.3363636363636" style="1" customWidth="1"/>
     <col min="31" max="31" width="11" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1" spans="1:31">
-      <c r="A1" s="10" t="s">
-        <v>0</v>
-      </c>
+      <c r="A1" s="10"/>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
       <c r="D1" s="11"/>
@@ -3606,7 +3605,7 @@
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:31">
       <c r="A2" s="12" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2" s="13"/>
       <c r="C2" s="14"/>
@@ -3616,7 +3615,7 @@
       <c r="G2" s="13"/>
       <c r="H2" s="14"/>
       <c r="I2" s="16" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J2" s="17"/>
       <c r="K2" s="18"/>
@@ -3624,7 +3623,7 @@
       <c r="M2" s="13"/>
       <c r="N2" s="14"/>
       <c r="O2" s="20" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P2" s="13"/>
       <c r="Q2" s="14"/>
@@ -3632,13 +3631,13 @@
       <c r="S2" s="13"/>
       <c r="T2" s="14"/>
       <c r="U2" s="20" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V2" s="13"/>
       <c r="W2" s="14"/>
       <c r="X2" s="22"/>
       <c r="Y2" s="20" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z2" s="13"/>
       <c r="AA2" s="14"/>
@@ -3649,7 +3648,7 @@
     </row>
     <row r="3" ht="13.5" customHeight="1" spans="1:31">
       <c r="A3" s="25" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
@@ -3685,22 +3684,22 @@
     <row r="4" ht="18.75" customHeight="1" spans="1:31">
       <c r="A4" s="26"/>
       <c r="B4" s="27" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="27" t="s">
         <v>7</v>
-      </c>
-      <c r="C4" s="27" t="s">
-        <v>8</v>
       </c>
       <c r="D4" s="14"/>
       <c r="E4" s="28" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4" s="13"/>
       <c r="G4" s="27" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H4" s="14"/>
       <c r="I4" s="27" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J4" s="13"/>
       <c r="K4" s="13"/>
@@ -3720,36 +3719,34 @@
       <c r="Y4" s="13"/>
       <c r="Z4" s="14"/>
       <c r="AA4" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="AB4" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="AB4" s="27" t="s">
+      <c r="AC4" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="AC4" s="27" t="s">
+      <c r="AD4" s="27" t="s">
         <v>14</v>
-      </c>
-      <c r="AD4" s="27" t="s">
-        <v>15</v>
       </c>
       <c r="AE4" s="14"/>
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:31">
       <c r="A5" s="29"/>
       <c r="B5" s="27" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C5" s="30" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D5" s="14"/>
-      <c r="E5" s="28" t="s">
-        <v>17</v>
-      </c>
+      <c r="E5" s="28"/>
       <c r="F5" s="13"/>
       <c r="G5" s="27"/>
       <c r="H5" s="14"/>
       <c r="I5" s="26" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J5" s="13"/>
       <c r="K5" s="13"/>
@@ -3766,28 +3763,28 @@
       <c r="V5" s="13"/>
       <c r="W5" s="14"/>
       <c r="X5" s="26" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Y5" s="13"/>
       <c r="Z5" s="14"/>
       <c r="AA5" s="26" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AC5" s="26" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AD5" s="26" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE5" s="14"/>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:31">
       <c r="A6" s="25" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B6" s="14"/>
       <c r="C6" s="28" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="13"/>
@@ -3796,7 +3793,7 @@
       <c r="H6" s="13"/>
       <c r="I6" s="14"/>
       <c r="J6" s="27" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K6" s="13"/>
       <c r="L6" s="14"/>
@@ -3805,7 +3802,7 @@
       <c r="Q6" s="13"/>
       <c r="R6" s="14"/>
       <c r="S6" s="27" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="T6" s="14"/>
       <c r="U6" s="9"/>
@@ -3823,13 +3820,13 @@
       <c r="A7" s="26"/>
       <c r="B7" s="26"/>
       <c r="C7" s="28" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D7" s="13"/>
       <c r="E7" s="13"/>
       <c r="F7" s="34"/>
       <c r="G7" s="35" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H7" s="13"/>
       <c r="I7" s="13"/>
@@ -3840,7 +3837,7 @@
       <c r="N7" s="13"/>
       <c r="O7" s="14"/>
       <c r="P7" s="27" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Q7" s="13"/>
       <c r="R7" s="14"/>
@@ -3860,7 +3857,7 @@
     </row>
     <row r="8" ht="18.75" customHeight="1" spans="1:31">
       <c r="A8" s="37" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B8" s="13"/>
       <c r="C8" s="13"/>
@@ -3868,29 +3865,29 @@
       <c r="E8" s="13"/>
       <c r="F8" s="13"/>
       <c r="G8" s="27" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H8" s="13"/>
       <c r="I8" s="14"/>
       <c r="J8" s="27" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="K8" s="14"/>
       <c r="L8" s="35"/>
       <c r="M8" s="27" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="N8" s="14"/>
       <c r="O8" s="27">
         <v>0</v>
       </c>
       <c r="P8" s="27" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="Q8" s="13"/>
       <c r="R8" s="14"/>
       <c r="S8" s="38" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T8" s="13"/>
       <c r="U8" s="13"/>
@@ -3913,16 +3910,16 @@
       <c r="E9" s="13"/>
       <c r="F9" s="13"/>
       <c r="G9" s="27" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H9" s="13"/>
       <c r="I9" s="14"/>
       <c r="J9" s="27" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="K9" s="14"/>
       <c r="M9" s="27" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="N9" s="14"/>
       <c r="O9" s="40" t="e">
@@ -3930,7 +3927,7 @@
         <v>#REF!</v>
       </c>
       <c r="P9" s="27" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="Q9" s="13"/>
       <c r="R9" s="14"/>
@@ -3950,7 +3947,7 @@
     </row>
     <row r="10" ht="17.5" customHeight="1" spans="1:31">
       <c r="A10" s="25" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B10" s="14"/>
       <c r="C10" s="26"/>
@@ -3985,27 +3982,27 @@
     </row>
     <row r="11" ht="17.5" customHeight="1" spans="1:31">
       <c r="A11" s="27" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B11" s="41"/>
       <c r="C11" s="28" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D11" s="13"/>
       <c r="E11" s="13"/>
       <c r="F11" s="13"/>
       <c r="G11" s="27" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H11" s="13"/>
       <c r="I11" s="14"/>
       <c r="J11" s="27" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K11" s="13"/>
       <c r="L11" s="14"/>
       <c r="M11" s="27" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N11" s="14"/>
       <c r="O11" s="26"/>
@@ -4015,12 +4012,12 @@
       <c r="S11" s="13"/>
       <c r="T11" s="14"/>
       <c r="U11" s="27" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V11" s="13"/>
       <c r="W11" s="14"/>
       <c r="X11" s="27" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Y11" s="14"/>
       <c r="Z11" s="42"/>
@@ -4034,7 +4031,7 @@
       <c r="A12" s="45"/>
       <c r="B12" s="46"/>
       <c r="C12" s="47" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="13"/>
@@ -4042,11 +4039,9 @@
       <c r="G12" s="48"/>
       <c r="H12" s="49"/>
       <c r="I12" s="47" t="s">
-        <v>38</v>
-      </c>
-      <c r="J12" s="50">
-        <v>0.0165079365079365</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="J12" s="50"/>
       <c r="K12" s="13"/>
       <c r="L12" s="14"/>
       <c r="M12" s="51">
@@ -4055,12 +4050,12 @@
       <c r="N12" s="14"/>
       <c r="O12" s="52"/>
       <c r="P12" s="27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Q12" s="53"/>
       <c r="R12" s="41"/>
       <c r="S12" s="54" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="T12" s="41"/>
       <c r="U12" s="27"/>
@@ -4079,7 +4074,7 @@
       <c r="A13" s="45"/>
       <c r="B13" s="46"/>
       <c r="C13" s="47" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D13" s="13"/>
       <c r="E13" s="13"/>
@@ -4087,11 +4082,9 @@
       <c r="G13" s="58"/>
       <c r="H13" s="59"/>
       <c r="I13" s="47" t="s">
-        <v>38</v>
-      </c>
-      <c r="J13" s="50">
-        <v>0.00761904761904762</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="J13" s="50"/>
       <c r="K13" s="13"/>
       <c r="L13" s="14"/>
       <c r="M13" s="51">
@@ -4102,7 +4095,7 @@
       <c r="P13" s="45"/>
       <c r="R13" s="46"/>
       <c r="S13" s="60" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="T13" s="46"/>
       <c r="U13" s="27"/>
@@ -4121,7 +4114,7 @@
       <c r="A14" s="45"/>
       <c r="B14" s="46"/>
       <c r="C14" s="47" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D14" s="13"/>
       <c r="E14" s="13"/>
@@ -4129,11 +4122,9 @@
       <c r="G14" s="48"/>
       <c r="H14" s="49"/>
       <c r="I14" s="47" t="s">
-        <v>38</v>
-      </c>
-      <c r="J14" s="50">
-        <v>0.0152380952380952</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="J14" s="50"/>
       <c r="K14" s="13"/>
       <c r="L14" s="14"/>
       <c r="M14" s="51">
@@ -4145,7 +4136,7 @@
       <c r="Q14" s="11"/>
       <c r="R14" s="63"/>
       <c r="S14" s="64" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="T14" s="63"/>
       <c r="U14" s="27"/>
@@ -4164,7 +4155,7 @@
       <c r="A15" s="45"/>
       <c r="B15" s="46"/>
       <c r="C15" s="47" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D15" s="13"/>
       <c r="E15" s="13"/>
@@ -4172,11 +4163,9 @@
       <c r="G15" s="65"/>
       <c r="H15" s="66"/>
       <c r="I15" s="47" t="s">
-        <v>38</v>
-      </c>
-      <c r="J15" s="50">
-        <v>0.00761904761904762</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="J15" s="50"/>
       <c r="K15" s="13"/>
       <c r="L15" s="14"/>
       <c r="M15" s="51">
@@ -4185,17 +4174,13 @@
       <c r="N15" s="14"/>
       <c r="O15" s="29"/>
       <c r="P15" s="27" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q15" s="13"/>
       <c r="R15" s="14"/>
-      <c r="S15" s="36" t="s">
-        <v>17</v>
-      </c>
+      <c r="S15" s="36"/>
       <c r="T15" s="14"/>
-      <c r="U15" s="67">
-        <v>288.84</v>
-      </c>
+      <c r="U15" s="67"/>
       <c r="V15" s="13"/>
       <c r="W15" s="13"/>
       <c r="X15" s="13"/>
@@ -4211,14 +4196,12 @@
       <c r="A16" s="45"/>
       <c r="B16" s="46"/>
       <c r="C16" s="47" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D16" s="13"/>
       <c r="E16" s="13"/>
       <c r="F16" s="14"/>
-      <c r="G16" s="47" t="s">
-        <v>17</v>
-      </c>
+      <c r="G16" s="47"/>
       <c r="H16" s="68"/>
       <c r="I16" s="13"/>
       <c r="J16" s="13"/>
@@ -4228,17 +4211,13 @@
       <c r="N16" s="71"/>
       <c r="O16" s="26"/>
       <c r="P16" s="27" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q16" s="13"/>
       <c r="R16" s="14"/>
-      <c r="S16" s="36" t="s">
-        <v>17</v>
-      </c>
+      <c r="S16" s="36"/>
       <c r="T16" s="14"/>
-      <c r="U16" s="67">
-        <v>35.36</v>
-      </c>
+      <c r="U16" s="67"/>
       <c r="V16" s="13"/>
       <c r="W16" s="13"/>
       <c r="X16" s="13"/>
@@ -4254,14 +4233,12 @@
       <c r="A17" s="45"/>
       <c r="B17" s="46"/>
       <c r="C17" s="47" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D17" s="13"/>
       <c r="E17" s="13"/>
       <c r="F17" s="14"/>
-      <c r="G17" s="47" t="s">
-        <v>17</v>
-      </c>
+      <c r="G17" s="47"/>
       <c r="H17" s="68"/>
       <c r="I17" s="13"/>
       <c r="J17" s="13"/>
@@ -4271,17 +4248,13 @@
       <c r="N17" s="71"/>
       <c r="O17" s="26"/>
       <c r="P17" s="27" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q17" s="13"/>
       <c r="R17" s="14"/>
-      <c r="S17" s="36" t="s">
-        <v>17</v>
-      </c>
+      <c r="S17" s="36"/>
       <c r="T17" s="14"/>
-      <c r="U17" s="40">
-        <v>0.0247619047619048</v>
-      </c>
+      <c r="U17" s="40"/>
       <c r="V17" s="13"/>
       <c r="W17" s="13"/>
       <c r="X17" s="13"/>
@@ -4297,14 +4270,12 @@
       <c r="A18" s="62"/>
       <c r="B18" s="63"/>
       <c r="C18" s="47" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D18" s="13"/>
       <c r="E18" s="13"/>
       <c r="F18" s="14"/>
-      <c r="G18" s="47" t="s">
-        <v>17</v>
-      </c>
+      <c r="G18" s="47"/>
       <c r="H18" s="68"/>
       <c r="I18" s="13"/>
       <c r="J18" s="13"/>
@@ -4314,23 +4285,19 @@
       <c r="N18" s="71"/>
       <c r="O18" s="26"/>
       <c r="P18" s="27" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Q18" s="13"/>
       <c r="R18" s="14"/>
-      <c r="S18" s="36" t="s">
-        <v>17</v>
-      </c>
+      <c r="S18" s="36"/>
       <c r="T18" s="14"/>
       <c r="U18" s="27" t="s">
-        <v>52</v>
-      </c>
-      <c r="V18" s="27">
-        <v>14</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="V18" s="27"/>
       <c r="W18" s="14"/>
       <c r="X18" s="27" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Y18" s="27">
         <v>0</v>
@@ -4344,7 +4311,7 @@
     </row>
     <row r="19" ht="17.5" customHeight="1" spans="1:31">
       <c r="A19" s="25" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B19" s="14"/>
       <c r="C19" s="26"/>
@@ -4378,12 +4345,10 @@
       <c r="AE19" s="14"/>
     </row>
     <row r="20" ht="30" customHeight="1" spans="1:31">
-      <c r="A20" s="27" t="s">
-        <v>17</v>
-      </c>
+      <c r="A20" s="27"/>
       <c r="B20" s="41"/>
       <c r="C20" s="75" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D20" s="13"/>
       <c r="E20" s="13"/>
@@ -4418,7 +4383,7 @@
       <c r="A21" s="45"/>
       <c r="B21" s="46"/>
       <c r="C21" s="39" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D21" s="13"/>
       <c r="E21" s="13"/>
@@ -4432,10 +4397,10 @@
       <c r="M21" s="13"/>
       <c r="N21" s="13"/>
       <c r="O21" s="26" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P21" s="78" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Q21" s="13"/>
       <c r="R21" s="13"/>
@@ -4453,55 +4418,55 @@
       <c r="AD21" s="77"/>
       <c r="AE21" s="78"/>
     </row>
-    <row r="22" ht="42" customHeight="1" spans="1:31">
+    <row r="22" ht="60" customHeight="1" spans="1:31">
       <c r="A22" s="45"/>
       <c r="B22" s="46"/>
       <c r="C22" s="79" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D22" s="68"/>
       <c r="E22" s="14"/>
       <c r="F22" s="79" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G22" s="68"/>
       <c r="H22" s="14"/>
       <c r="I22" s="79" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J22" s="68"/>
       <c r="K22" s="14"/>
       <c r="L22" s="79" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="M22" s="68"/>
       <c r="N22" s="14"/>
       <c r="O22" s="52"/>
       <c r="P22" s="79" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q22" s="68"/>
       <c r="R22" s="14"/>
       <c r="S22" s="79" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="T22" s="68"/>
       <c r="U22" s="14"/>
       <c r="V22" s="79" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="W22" s="68"/>
       <c r="X22" s="14"/>
       <c r="Y22" s="79" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Z22" s="68"/>
       <c r="AA22" s="14"/>
       <c r="AB22" s="80" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC22" s="81" t="s">
         <v>62</v>
-      </c>
-      <c r="AC22" s="81" t="s">
-        <v>63</v>
       </c>
       <c r="AD22" s="82"/>
       <c r="AE22" s="71"/>
@@ -4510,10 +4475,10 @@
       <c r="A23" s="45"/>
       <c r="B23" s="46"/>
       <c r="C23" s="47" t="s">
+        <v>63</v>
+      </c>
+      <c r="D23" s="83" t="s">
         <v>64</v>
-      </c>
-      <c r="D23" s="83" t="s">
-        <v>65</v>
       </c>
       <c r="E23" s="13"/>
       <c r="F23" s="13"/>
@@ -4527,10 +4492,10 @@
       <c r="N23" s="14"/>
       <c r="O23" s="52"/>
       <c r="P23" s="47" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="Q23" s="83" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R23" s="13"/>
       <c r="S23" s="13"/>
@@ -4544,7 +4509,7 @@
       <c r="AA23" s="14"/>
       <c r="AB23" s="46"/>
       <c r="AC23" s="81" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AD23" s="82"/>
       <c r="AE23" s="71"/>
@@ -4553,56 +4518,56 @@
       <c r="A24" s="45"/>
       <c r="B24" s="46"/>
       <c r="C24" s="47" t="s">
+        <v>67</v>
+      </c>
+      <c r="D24" s="47" t="s">
         <v>68</v>
       </c>
-      <c r="D24" s="47" t="s">
+      <c r="E24" s="47" t="s">
         <v>69</v>
-      </c>
-      <c r="E24" s="47" t="s">
-        <v>70</v>
       </c>
       <c r="F24" s="13"/>
       <c r="G24" s="14"/>
       <c r="H24" s="47" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I24" s="14"/>
       <c r="J24" s="47" t="s">
+        <v>71</v>
+      </c>
+      <c r="K24" s="47" t="s">
         <v>72</v>
-      </c>
-      <c r="K24" s="47" t="s">
-        <v>73</v>
       </c>
       <c r="L24" s="13"/>
       <c r="M24" s="13"/>
       <c r="N24" s="14"/>
       <c r="O24" s="52"/>
       <c r="P24" s="47" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q24" s="47" t="s">
         <v>68</v>
       </c>
-      <c r="Q24" s="47" t="s">
+      <c r="R24" s="47" t="s">
         <v>69</v>
-      </c>
-      <c r="R24" s="47" t="s">
-        <v>70</v>
       </c>
       <c r="S24" s="13"/>
       <c r="T24" s="14"/>
       <c r="U24" s="47" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="V24" s="14"/>
       <c r="W24" s="47" t="s">
+        <v>71</v>
+      </c>
+      <c r="X24" s="47" t="s">
         <v>72</v>
-      </c>
-      <c r="X24" s="47" t="s">
-        <v>73</v>
       </c>
       <c r="Y24" s="13"/>
       <c r="Z24" s="13"/>
       <c r="AA24" s="14"/>
       <c r="AB24" s="84" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AC24" s="85"/>
       <c r="AD24" s="70"/>
@@ -4612,64 +4577,60 @@
       <c r="A25" s="45"/>
       <c r="B25" s="46"/>
       <c r="C25" s="86" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D25" s="87" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E25" s="68" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F25" s="13"/>
       <c r="G25" s="14"/>
       <c r="H25" s="68" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I25" s="14"/>
       <c r="J25" s="68" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K25" s="79" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="L25" s="83"/>
       <c r="M25" s="79" t="s">
-        <v>77</v>
-      </c>
-      <c r="N25" s="83">
-        <v>0.32</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="N25" s="83"/>
       <c r="O25" s="52"/>
       <c r="P25" s="86" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q25" s="87" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R25" s="68" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="S25" s="13"/>
       <c r="T25" s="14"/>
       <c r="U25" s="68" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V25" s="14"/>
       <c r="W25" s="68" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="X25" s="79" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Y25" s="83"/>
       <c r="Z25" s="79" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA25" s="83"/>
+      <c r="AB25" s="84" t="s">
         <v>77</v>
-      </c>
-      <c r="AA25" s="83">
-        <v>0.34</v>
-      </c>
-      <c r="AB25" s="84" t="s">
-        <v>78</v>
       </c>
       <c r="AC25" s="82"/>
       <c r="AD25" s="70"/>
@@ -4679,76 +4640,64 @@
       <c r="A26" s="45"/>
       <c r="B26" s="46"/>
       <c r="C26" s="79" t="s">
+        <v>78</v>
+      </c>
+      <c r="D26" s="83" t="s">
+        <v>15</v>
+      </c>
+      <c r="E26" s="47" t="s">
         <v>79</v>
       </c>
-      <c r="D26" s="83" t="s">
-        <v>16</v>
-      </c>
-      <c r="E26" s="47" t="s">
+      <c r="F26" s="68" t="s">
         <v>80</v>
       </c>
-      <c r="F26" s="68" t="s">
+      <c r="G26" s="68" t="s">
         <v>81</v>
       </c>
-      <c r="G26" s="68" t="s">
+      <c r="H26" s="47" t="s">
+        <v>79</v>
+      </c>
+      <c r="I26" s="68"/>
+      <c r="J26" s="68"/>
+      <c r="K26" s="79" t="s">
         <v>82</v>
-      </c>
-      <c r="H26" s="47" t="s">
-        <v>80</v>
-      </c>
-      <c r="I26" s="68">
-        <v>24.7</v>
-      </c>
-      <c r="J26" s="68">
-        <v>24.7</v>
-      </c>
-      <c r="K26" s="79" t="s">
-        <v>83</v>
       </c>
       <c r="L26" s="68"/>
       <c r="M26" s="79" t="s">
-        <v>84</v>
-      </c>
-      <c r="N26" s="88">
-        <v>0.3</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="N26" s="88"/>
       <c r="O26" s="52"/>
       <c r="P26" s="79" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q26" s="83" t="s">
+        <v>15</v>
+      </c>
+      <c r="R26" s="47" t="s">
         <v>79</v>
       </c>
-      <c r="Q26" s="83" t="s">
-        <v>16</v>
-      </c>
-      <c r="R26" s="47" t="s">
+      <c r="S26" s="68" t="s">
         <v>80</v>
       </c>
-      <c r="S26" s="68" t="s">
+      <c r="T26" s="68" t="s">
         <v>81</v>
       </c>
-      <c r="T26" s="68" t="s">
+      <c r="U26" s="47" t="s">
+        <v>79</v>
+      </c>
+      <c r="V26" s="68"/>
+      <c r="W26" s="68"/>
+      <c r="X26" s="79" t="s">
         <v>82</v>
-      </c>
-      <c r="U26" s="47" t="s">
-        <v>80</v>
-      </c>
-      <c r="V26" s="68">
-        <v>24.6</v>
-      </c>
-      <c r="W26" s="68">
-        <v>25</v>
-      </c>
-      <c r="X26" s="79" t="s">
-        <v>83</v>
       </c>
       <c r="Y26" s="89"/>
       <c r="Z26" s="79" t="s">
+        <v>83</v>
+      </c>
+      <c r="AA26" s="88"/>
+      <c r="AB26" s="84" t="s">
         <v>84</v>
-      </c>
-      <c r="AA26" s="88">
-        <v>0.32</v>
-      </c>
-      <c r="AB26" s="84" t="s">
-        <v>85</v>
       </c>
       <c r="AC26" s="82"/>
       <c r="AD26" s="90"/>
@@ -4760,12 +4709,8 @@
       <c r="C27" s="29"/>
       <c r="D27" s="29"/>
       <c r="E27" s="29"/>
-      <c r="F27" s="68">
-        <v>0</v>
-      </c>
-      <c r="G27" s="89">
-        <v>0</v>
-      </c>
+      <c r="F27" s="68"/>
+      <c r="G27" s="89"/>
       <c r="H27" s="29"/>
       <c r="I27" s="29"/>
       <c r="J27" s="29"/>
@@ -4777,12 +4722,8 @@
       <c r="P27" s="29"/>
       <c r="Q27" s="29"/>
       <c r="R27" s="29"/>
-      <c r="S27" s="68">
-        <v>0</v>
-      </c>
-      <c r="T27" s="68">
-        <v>0</v>
-      </c>
+      <c r="S27" s="68"/>
+      <c r="T27" s="68"/>
       <c r="U27" s="29"/>
       <c r="V27" s="29"/>
       <c r="W27" s="29"/>
@@ -4799,74 +4740,62 @@
       <c r="A28" s="45"/>
       <c r="B28" s="46"/>
       <c r="C28" s="79" t="s">
+        <v>85</v>
+      </c>
+      <c r="D28" s="87" t="s">
+        <v>15</v>
+      </c>
+      <c r="E28" s="79" t="s">
         <v>86</v>
       </c>
-      <c r="D28" s="87" t="s">
-        <v>16</v>
-      </c>
-      <c r="E28" s="79" t="s">
-        <v>87</v>
-      </c>
-      <c r="F28" s="68">
-        <v>18</v>
-      </c>
+      <c r="F28" s="68"/>
       <c r="G28" s="14"/>
       <c r="H28" s="79" t="s">
+        <v>87</v>
+      </c>
+      <c r="I28" s="95"/>
+      <c r="J28" s="95"/>
+      <c r="K28" s="79" t="s">
         <v>88</v>
-      </c>
-      <c r="I28" s="95">
-        <v>0.28</v>
-      </c>
-      <c r="J28" s="95">
-        <v>0.26</v>
-      </c>
-      <c r="K28" s="79" t="s">
-        <v>89</v>
       </c>
       <c r="L28" s="83"/>
       <c r="M28" s="79" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N28" s="83">
         <f>N25-N26</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="O28" s="52"/>
       <c r="P28" s="79" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q28" s="87" t="s">
+        <v>15</v>
+      </c>
+      <c r="R28" s="79" t="s">
         <v>86</v>
       </c>
-      <c r="Q28" s="87" t="s">
-        <v>16</v>
-      </c>
-      <c r="R28" s="79" t="s">
-        <v>87</v>
-      </c>
-      <c r="S28" s="68">
-        <v>18</v>
-      </c>
+      <c r="S28" s="68"/>
       <c r="T28" s="14"/>
       <c r="U28" s="79" t="s">
+        <v>87</v>
+      </c>
+      <c r="V28" s="95"/>
+      <c r="W28" s="68"/>
+      <c r="X28" s="79" t="s">
         <v>88</v>
-      </c>
-      <c r="V28" s="95">
-        <v>0.28</v>
-      </c>
-      <c r="W28" s="68">
-        <v>0.26</v>
-      </c>
-      <c r="X28" s="79" t="s">
-        <v>89</v>
       </c>
       <c r="Y28" s="96"/>
       <c r="Z28" s="79" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AA28" s="83">
         <f>AA25-AA26</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AB28" s="84" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="AC28" s="82"/>
       <c r="AD28" s="70"/>
@@ -4876,68 +4805,56 @@
       <c r="A29" s="45"/>
       <c r="B29" s="46"/>
       <c r="C29" s="79" t="s">
+        <v>91</v>
+      </c>
+      <c r="D29" s="87" t="s">
+        <v>15</v>
+      </c>
+      <c r="E29" s="79" t="s">
         <v>92</v>
-      </c>
-      <c r="D29" s="87" t="s">
-        <v>16</v>
-      </c>
-      <c r="E29" s="79" t="s">
-        <v>93</v>
       </c>
       <c r="F29" s="89"/>
       <c r="G29" s="14"/>
       <c r="H29" s="79" t="s">
+        <v>93</v>
+      </c>
+      <c r="I29" s="68"/>
+      <c r="J29" s="68"/>
+      <c r="K29" s="79" t="s">
         <v>94</v>
-      </c>
-      <c r="I29" s="68">
-        <v>0.36</v>
-      </c>
-      <c r="J29" s="68">
-        <v>0.32</v>
-      </c>
-      <c r="K29" s="79" t="s">
-        <v>95</v>
       </c>
       <c r="L29" s="83"/>
       <c r="M29" s="79" t="s">
-        <v>96</v>
-      </c>
-      <c r="N29" s="83">
-        <v>0.3</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="N29" s="83"/>
       <c r="O29" s="52"/>
       <c r="P29" s="79" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q29" s="87" t="s">
+        <v>15</v>
+      </c>
+      <c r="R29" s="79" t="s">
         <v>92</v>
-      </c>
-      <c r="Q29" s="87" t="s">
-        <v>16</v>
-      </c>
-      <c r="R29" s="79" t="s">
-        <v>93</v>
       </c>
       <c r="S29" s="89"/>
       <c r="T29" s="14"/>
       <c r="U29" s="79" t="s">
+        <v>93</v>
+      </c>
+      <c r="V29" s="68"/>
+      <c r="W29" s="68"/>
+      <c r="X29" s="79" t="s">
         <v>94</v>
-      </c>
-      <c r="V29" s="68">
-        <v>0.38</v>
-      </c>
-      <c r="W29" s="68">
-        <v>0.32</v>
-      </c>
-      <c r="X29" s="79" t="s">
-        <v>95</v>
       </c>
       <c r="Y29" s="83"/>
       <c r="Z29" s="79" t="s">
+        <v>95</v>
+      </c>
+      <c r="AA29" s="83"/>
+      <c r="AB29" s="84" t="s">
         <v>96</v>
-      </c>
-      <c r="AA29" s="83">
-        <v>0.3</v>
-      </c>
-      <c r="AB29" s="84" t="s">
-        <v>97</v>
       </c>
       <c r="AC29" s="82"/>
       <c r="AD29" s="70"/>
@@ -4947,66 +4864,62 @@
       <c r="A30" s="45"/>
       <c r="B30" s="46"/>
       <c r="C30" s="79" t="s">
+        <v>97</v>
+      </c>
+      <c r="D30" s="87" t="s">
+        <v>15</v>
+      </c>
+      <c r="E30" s="79" t="s">
         <v>98</v>
-      </c>
-      <c r="D30" s="87" t="s">
-        <v>16</v>
-      </c>
-      <c r="E30" s="79" t="s">
-        <v>99</v>
       </c>
       <c r="F30" s="68"/>
       <c r="G30" s="14"/>
       <c r="H30" s="79" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I30" s="68"/>
       <c r="J30" s="14"/>
       <c r="K30" s="79" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L30" s="68">
         <f>L29-L25</f>
         <v>0</v>
       </c>
       <c r="M30" s="79" t="s">
-        <v>102</v>
-      </c>
-      <c r="N30" s="83">
-        <v>0.28</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="N30" s="83"/>
       <c r="O30" s="52"/>
       <c r="P30" s="79" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q30" s="87" t="s">
+        <v>15</v>
+      </c>
+      <c r="R30" s="79" t="s">
         <v>98</v>
-      </c>
-      <c r="Q30" s="87" t="s">
-        <v>16</v>
-      </c>
-      <c r="R30" s="79" t="s">
-        <v>99</v>
       </c>
       <c r="S30" s="68"/>
       <c r="T30" s="14"/>
       <c r="U30" s="79" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="V30" s="68"/>
       <c r="W30" s="14"/>
       <c r="X30" s="79" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="Y30" s="68">
         <f>Y29-Y25</f>
         <v>0</v>
       </c>
       <c r="Z30" s="79" t="s">
+        <v>101</v>
+      </c>
+      <c r="AA30" s="83"/>
+      <c r="AB30" s="97" t="s">
         <v>102</v>
-      </c>
-      <c r="AA30" s="83">
-        <v>0.29</v>
-      </c>
-      <c r="AB30" s="97" t="s">
-        <v>103</v>
       </c>
       <c r="AC30" s="53"/>
       <c r="AD30" s="53"/>
@@ -5016,51 +4929,51 @@
       <c r="A31" s="45"/>
       <c r="B31" s="46"/>
       <c r="C31" s="79" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D31" s="87" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E31" s="98"/>
       <c r="F31" s="79"/>
       <c r="G31" s="14"/>
       <c r="H31" s="79" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I31" s="68"/>
       <c r="J31" s="14"/>
       <c r="K31" s="79"/>
       <c r="L31" s="79"/>
       <c r="M31" s="79" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N31" s="68">
         <f>N29-N30</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="O31" s="52"/>
       <c r="P31" s="79" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="Q31" s="87" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R31" s="98"/>
       <c r="S31" s="79"/>
       <c r="T31" s="14"/>
       <c r="U31" s="79" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="V31" s="68"/>
       <c r="W31" s="14"/>
       <c r="X31" s="79"/>
       <c r="Y31" s="79"/>
       <c r="Z31" s="79" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AA31" s="68">
         <f>AA29-AA30</f>
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="AE31" s="46"/>
     </row>
@@ -5101,10 +5014,10 @@
       <c r="A33" s="45"/>
       <c r="B33" s="46"/>
       <c r="C33" s="27" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D33" s="87" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E33" s="13"/>
       <c r="F33" s="13"/>
@@ -5118,10 +5031,10 @@
       <c r="N33" s="14"/>
       <c r="O33" s="52"/>
       <c r="P33" s="36" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="Q33" s="87" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="R33" s="13"/>
       <c r="S33" s="13"/>
@@ -5134,11 +5047,11 @@
       <c r="Z33" s="13"/>
       <c r="AA33" s="14"/>
       <c r="AB33" s="84" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AC33" s="14"/>
       <c r="AD33" s="99" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AE33" s="14"/>
     </row>
@@ -5146,60 +5059,60 @@
       <c r="A34" s="45"/>
       <c r="B34" s="46"/>
       <c r="C34" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="D34" s="27" t="s">
         <v>68</v>
       </c>
-      <c r="D34" s="27" t="s">
+      <c r="E34" s="27" t="s">
         <v>69</v>
-      </c>
-      <c r="E34" s="27" t="s">
-        <v>70</v>
       </c>
       <c r="F34" s="13"/>
       <c r="G34" s="14"/>
       <c r="H34" s="27" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I34" s="14"/>
       <c r="J34" s="27" t="s">
+        <v>71</v>
+      </c>
+      <c r="K34" s="27" t="s">
         <v>72</v>
-      </c>
-      <c r="K34" s="27" t="s">
-        <v>73</v>
       </c>
       <c r="L34" s="13"/>
       <c r="M34" s="13"/>
       <c r="N34" s="14"/>
       <c r="O34" s="52"/>
       <c r="P34" s="36" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q34" s="27" t="s">
         <v>68</v>
       </c>
-      <c r="Q34" s="27" t="s">
+      <c r="R34" s="27" t="s">
         <v>69</v>
-      </c>
-      <c r="R34" s="27" t="s">
-        <v>70</v>
       </c>
       <c r="S34" s="13"/>
       <c r="T34" s="14"/>
       <c r="U34" s="27" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="V34" s="14"/>
       <c r="W34" s="27" t="s">
+        <v>71</v>
+      </c>
+      <c r="X34" s="27" t="s">
         <v>72</v>
-      </c>
-      <c r="X34" s="27" t="s">
-        <v>73</v>
       </c>
       <c r="Y34" s="13"/>
       <c r="Z34" s="13"/>
       <c r="AA34" s="14"/>
       <c r="AB34" s="84" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AC34" s="14"/>
       <c r="AD34" s="99" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AE34" s="14"/>
     </row>
@@ -5207,72 +5120,72 @@
       <c r="A35" s="45"/>
       <c r="B35" s="46"/>
       <c r="C35" s="100" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D35" s="87" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E35" s="101" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F35" s="13"/>
       <c r="G35" s="14"/>
       <c r="H35" s="101" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I35" s="14"/>
       <c r="J35" s="101" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K35" s="99" t="s">
+        <v>75</v>
+      </c>
+      <c r="L35" s="101" t="s">
+        <v>15</v>
+      </c>
+      <c r="M35" s="99" t="s">
         <v>76</v>
       </c>
-      <c r="L35" s="101" t="s">
-        <v>16</v>
-      </c>
-      <c r="M35" s="99" t="s">
-        <v>77</v>
-      </c>
       <c r="N35" s="102" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O35" s="52"/>
       <c r="P35" s="100" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q35" s="87" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R35" s="101" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="S35" s="13"/>
       <c r="T35" s="14"/>
       <c r="U35" s="101" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V35" s="14"/>
       <c r="W35" s="101" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="X35" s="99" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y35" s="101" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z35" s="99" t="s">
         <v>76</v>
       </c>
-      <c r="Y35" s="101" t="s">
-        <v>16</v>
-      </c>
-      <c r="Z35" s="99" t="s">
-        <v>77</v>
-      </c>
       <c r="AA35" s="101" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AB35" s="84" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AC35" s="14"/>
       <c r="AD35" s="103" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AE35" s="14"/>
     </row>
@@ -5280,84 +5193,84 @@
       <c r="A36" s="45"/>
       <c r="B36" s="46"/>
       <c r="C36" s="99" t="s">
+        <v>78</v>
+      </c>
+      <c r="D36" s="104" t="s">
+        <v>15</v>
+      </c>
+      <c r="E36" s="27" t="s">
         <v>79</v>
       </c>
-      <c r="D36" s="104" t="s">
-        <v>16</v>
-      </c>
-      <c r="E36" s="27" t="s">
+      <c r="F36" s="101" t="s">
         <v>80</v>
       </c>
-      <c r="F36" s="101" t="s">
+      <c r="G36" s="101" t="s">
         <v>81</v>
       </c>
-      <c r="G36" s="101" t="s">
+      <c r="H36" s="27" t="s">
+        <v>79</v>
+      </c>
+      <c r="I36" s="101" t="s">
+        <v>15</v>
+      </c>
+      <c r="J36" s="101" t="s">
+        <v>15</v>
+      </c>
+      <c r="K36" s="99" t="s">
         <v>82</v>
       </c>
-      <c r="H36" s="27" t="s">
-        <v>80</v>
-      </c>
-      <c r="I36" s="101" t="s">
-        <v>16</v>
-      </c>
-      <c r="J36" s="101" t="s">
-        <v>16</v>
-      </c>
-      <c r="K36" s="99" t="s">
+      <c r="L36" s="101" t="s">
+        <v>15</v>
+      </c>
+      <c r="M36" s="99" t="s">
         <v>83</v>
       </c>
-      <c r="L36" s="101" t="s">
-        <v>16</v>
-      </c>
-      <c r="M36" s="99" t="s">
-        <v>84</v>
-      </c>
       <c r="N36" s="102" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O36" s="52"/>
       <c r="P36" s="99" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q36" s="104" t="s">
+        <v>15</v>
+      </c>
+      <c r="R36" s="27" t="s">
         <v>79</v>
       </c>
-      <c r="Q36" s="104" t="s">
-        <v>16</v>
-      </c>
-      <c r="R36" s="27" t="s">
+      <c r="S36" s="101" t="s">
         <v>80</v>
       </c>
-      <c r="S36" s="101" t="s">
+      <c r="T36" s="101" t="s">
         <v>81</v>
       </c>
-      <c r="T36" s="101" t="s">
+      <c r="U36" s="27" t="s">
+        <v>79</v>
+      </c>
+      <c r="V36" s="101" t="s">
+        <v>15</v>
+      </c>
+      <c r="W36" s="101" t="s">
+        <v>15</v>
+      </c>
+      <c r="X36" s="99" t="s">
         <v>82</v>
       </c>
-      <c r="U36" s="27" t="s">
-        <v>80</v>
-      </c>
-      <c r="V36" s="101" t="s">
-        <v>16</v>
-      </c>
-      <c r="W36" s="101" t="s">
-        <v>16</v>
-      </c>
-      <c r="X36" s="99" t="s">
+      <c r="Y36" s="101" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z36" s="99" t="s">
         <v>83</v>
       </c>
-      <c r="Y36" s="101" t="s">
-        <v>16</v>
-      </c>
-      <c r="Z36" s="99" t="s">
-        <v>84</v>
-      </c>
       <c r="AA36" s="101" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AB36" s="84" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AC36" s="41"/>
       <c r="AD36" s="99" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AE36" s="41"/>
     </row>
@@ -5368,10 +5281,10 @@
       <c r="D37" s="29"/>
       <c r="E37" s="29"/>
       <c r="F37" s="101" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G37" s="101" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H37" s="29"/>
       <c r="I37" s="29"/>
@@ -5385,10 +5298,10 @@
       <c r="Q37" s="29"/>
       <c r="R37" s="29"/>
       <c r="S37" s="101" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T37" s="101" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U37" s="29"/>
       <c r="V37" s="29"/>
@@ -5406,80 +5319,80 @@
       <c r="A38" s="45"/>
       <c r="B38" s="46"/>
       <c r="C38" s="99" t="s">
+        <v>85</v>
+      </c>
+      <c r="D38" s="87" t="s">
+        <v>15</v>
+      </c>
+      <c r="E38" s="99" t="s">
         <v>86</v>
       </c>
-      <c r="D38" s="87" t="s">
-        <v>16</v>
-      </c>
-      <c r="E38" s="99" t="s">
-        <v>87</v>
-      </c>
       <c r="F38" s="101" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G38" s="14"/>
       <c r="H38" s="99" t="s">
+        <v>87</v>
+      </c>
+      <c r="I38" s="101" t="s">
+        <v>15</v>
+      </c>
+      <c r="J38" s="101" t="s">
+        <v>15</v>
+      </c>
+      <c r="K38" s="99" t="s">
         <v>88</v>
       </c>
-      <c r="I38" s="101" t="s">
-        <v>16</v>
-      </c>
-      <c r="J38" s="101" t="s">
-        <v>16</v>
-      </c>
-      <c r="K38" s="99" t="s">
+      <c r="L38" s="101" t="s">
+        <v>15</v>
+      </c>
+      <c r="M38" s="99" t="s">
         <v>89</v>
-      </c>
-      <c r="L38" s="101" t="s">
-        <v>16</v>
-      </c>
-      <c r="M38" s="99" t="s">
-        <v>90</v>
       </c>
       <c r="N38" s="102" t="e">
         <v>#VALUE!</v>
       </c>
       <c r="O38" s="52"/>
       <c r="P38" s="99" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q38" s="87" t="s">
+        <v>15</v>
+      </c>
+      <c r="R38" s="99" t="s">
         <v>86</v>
       </c>
-      <c r="Q38" s="87" t="s">
-        <v>16</v>
-      </c>
-      <c r="R38" s="99" t="s">
-        <v>87</v>
-      </c>
       <c r="S38" s="101" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T38" s="14"/>
       <c r="U38" s="99" t="s">
+        <v>87</v>
+      </c>
+      <c r="V38" s="101" t="s">
+        <v>15</v>
+      </c>
+      <c r="W38" s="101" t="s">
+        <v>15</v>
+      </c>
+      <c r="X38" s="99" t="s">
         <v>88</v>
       </c>
-      <c r="V38" s="101" t="s">
-        <v>16</v>
-      </c>
-      <c r="W38" s="101" t="s">
-        <v>16</v>
-      </c>
-      <c r="X38" s="99" t="s">
+      <c r="Y38" s="101" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z38" s="99" t="s">
         <v>89</v>
-      </c>
-      <c r="Y38" s="101" t="s">
-        <v>16</v>
-      </c>
-      <c r="Z38" s="99" t="s">
-        <v>90</v>
       </c>
       <c r="AA38" s="101" t="e">
         <v>#VALUE!</v>
       </c>
       <c r="AB38" s="84" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AC38" s="14"/>
       <c r="AD38" s="99" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AE38" s="14"/>
     </row>
@@ -5487,80 +5400,80 @@
       <c r="A39" s="45"/>
       <c r="B39" s="46"/>
       <c r="C39" s="99" t="s">
+        <v>91</v>
+      </c>
+      <c r="D39" s="87" t="s">
+        <v>15</v>
+      </c>
+      <c r="E39" s="99" t="s">
         <v>92</v>
       </c>
-      <c r="D39" s="87" t="s">
-        <v>16</v>
-      </c>
-      <c r="E39" s="99" t="s">
-        <v>93</v>
-      </c>
       <c r="F39" s="101" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G39" s="14"/>
       <c r="H39" s="99" t="s">
+        <v>93</v>
+      </c>
+      <c r="I39" s="101" t="s">
+        <v>15</v>
+      </c>
+      <c r="J39" s="101" t="s">
+        <v>15</v>
+      </c>
+      <c r="K39" s="99" t="s">
         <v>94</v>
       </c>
-      <c r="I39" s="101" t="s">
-        <v>16</v>
-      </c>
-      <c r="J39" s="101" t="s">
-        <v>16</v>
-      </c>
-      <c r="K39" s="99" t="s">
+      <c r="L39" s="101" t="s">
+        <v>15</v>
+      </c>
+      <c r="M39" s="99" t="s">
         <v>95</v>
       </c>
-      <c r="L39" s="101" t="s">
-        <v>16</v>
-      </c>
-      <c r="M39" s="99" t="s">
-        <v>96</v>
-      </c>
       <c r="N39" s="102" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O39" s="52"/>
       <c r="P39" s="99" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q39" s="87" t="s">
+        <v>15</v>
+      </c>
+      <c r="R39" s="99" t="s">
         <v>92</v>
       </c>
-      <c r="Q39" s="87" t="s">
-        <v>16</v>
-      </c>
-      <c r="R39" s="99" t="s">
-        <v>93</v>
-      </c>
       <c r="S39" s="101" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T39" s="14"/>
       <c r="U39" s="99" t="s">
+        <v>93</v>
+      </c>
+      <c r="V39" s="101" t="s">
+        <v>15</v>
+      </c>
+      <c r="W39" s="101" t="s">
+        <v>15</v>
+      </c>
+      <c r="X39" s="99" t="s">
         <v>94</v>
       </c>
-      <c r="V39" s="101" t="s">
-        <v>16</v>
-      </c>
-      <c r="W39" s="101" t="s">
-        <v>16</v>
-      </c>
-      <c r="X39" s="99" t="s">
+      <c r="Y39" s="101" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z39" s="99" t="s">
         <v>95</v>
       </c>
-      <c r="Y39" s="101" t="s">
-        <v>16</v>
-      </c>
-      <c r="Z39" s="99" t="s">
-        <v>96</v>
-      </c>
       <c r="AA39" s="101" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AB39" s="84" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AC39" s="14"/>
       <c r="AD39" s="99" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="AE39" s="14"/>
     </row>
@@ -5568,76 +5481,76 @@
       <c r="A40" s="45"/>
       <c r="B40" s="46"/>
       <c r="C40" s="99" t="s">
+        <v>97</v>
+      </c>
+      <c r="D40" s="87" t="s">
+        <v>15</v>
+      </c>
+      <c r="E40" s="99" t="s">
         <v>98</v>
       </c>
-      <c r="D40" s="87" t="s">
-        <v>16</v>
-      </c>
-      <c r="E40" s="99" t="s">
-        <v>99</v>
-      </c>
       <c r="F40" s="101" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G40" s="14"/>
       <c r="H40" s="99" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I40" s="101" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J40" s="14"/>
       <c r="K40" s="99" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L40" s="101" t="e">
         <v>#VALUE!</v>
       </c>
       <c r="M40" s="99" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="N40" s="102" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O40" s="52"/>
       <c r="P40" s="99" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q40" s="87" t="s">
+        <v>15</v>
+      </c>
+      <c r="R40" s="99" t="s">
         <v>98</v>
       </c>
-      <c r="Q40" s="87" t="s">
-        <v>16</v>
-      </c>
-      <c r="R40" s="99" t="s">
-        <v>99</v>
-      </c>
       <c r="S40" s="101" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T40" s="14"/>
       <c r="U40" s="99" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="V40" s="101" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W40" s="14"/>
       <c r="X40" s="99" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="Y40" s="101" t="e">
         <v>#VALUE!</v>
       </c>
       <c r="Z40" s="99" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AA40" s="101" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AB40" s="84" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="AC40" s="14"/>
       <c r="AD40" s="99" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="AE40" s="14"/>
     </row>
@@ -5645,50 +5558,50 @@
       <c r="A41" s="45"/>
       <c r="B41" s="46"/>
       <c r="C41" s="99" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D41" s="87" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E41" s="99"/>
       <c r="F41" s="99"/>
       <c r="G41" s="99"/>
       <c r="H41" s="99" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I41" s="101" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J41" s="14"/>
       <c r="K41" s="99"/>
       <c r="L41" s="99"/>
       <c r="M41" s="99" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N41" s="102" t="e">
         <v>#VALUE!</v>
       </c>
       <c r="O41" s="52"/>
       <c r="P41" s="99" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="Q41" s="87" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R41" s="99"/>
       <c r="S41" s="99"/>
       <c r="T41" s="99"/>
       <c r="U41" s="99" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="V41" s="101" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W41" s="14"/>
       <c r="X41" s="99"/>
       <c r="Y41" s="99"/>
       <c r="Z41" s="99" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AA41" s="101" t="e">
         <v>#VALUE!</v>
@@ -5702,10 +5615,10 @@
       <c r="A42" s="45"/>
       <c r="B42" s="46"/>
       <c r="C42" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="D42" s="87" t="s">
         <v>118</v>
-      </c>
-      <c r="D42" s="87" t="s">
-        <v>119</v>
       </c>
       <c r="E42" s="13"/>
       <c r="F42" s="13"/>
@@ -5719,10 +5632,10 @@
       <c r="N42" s="14"/>
       <c r="O42" s="29"/>
       <c r="P42" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q42" s="87" t="s">
         <v>118</v>
-      </c>
-      <c r="Q42" s="87" t="s">
-        <v>119</v>
       </c>
       <c r="R42" s="13"/>
       <c r="S42" s="13"/>
@@ -5743,7 +5656,7 @@
       <c r="A43" s="45"/>
       <c r="B43" s="46"/>
       <c r="C43" s="75" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D43" s="13"/>
       <c r="E43" s="13"/>
@@ -5778,7 +5691,7 @@
       <c r="A44" s="45"/>
       <c r="B44" s="46"/>
       <c r="C44" s="26" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D44" s="13"/>
       <c r="E44" s="13"/>
@@ -5793,7 +5706,7 @@
       <c r="N44" s="14"/>
       <c r="O44" s="26"/>
       <c r="P44" s="26" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Q44" s="13"/>
       <c r="R44" s="13"/>
@@ -5815,28 +5728,28 @@
       <c r="A45" s="45"/>
       <c r="B45" s="46"/>
       <c r="C45" s="99" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D45" s="14"/>
       <c r="E45" s="101" t="s">
+        <v>121</v>
+      </c>
+      <c r="F45" s="99" t="s">
         <v>122</v>
-      </c>
-      <c r="F45" s="99" t="s">
-        <v>123</v>
       </c>
       <c r="G45" s="101">
         <v>0.09</v>
       </c>
       <c r="H45" s="14"/>
       <c r="I45" s="99" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J45" s="101">
         <v>0.089</v>
       </c>
       <c r="K45" s="14"/>
       <c r="L45" s="99" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M45" s="101">
         <v>0.09</v>
@@ -5844,28 +5757,28 @@
       <c r="N45" s="14"/>
       <c r="O45" s="52"/>
       <c r="P45" s="99" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="Q45" s="14"/>
       <c r="R45" s="101" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="S45" s="99" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="T45" s="101">
         <v>0.09</v>
       </c>
       <c r="U45" s="14"/>
       <c r="V45" s="99" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="W45" s="101">
         <v>0.089</v>
       </c>
       <c r="X45" s="14"/>
       <c r="Y45" s="99" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="Z45" s="101">
         <v>0.093</v>
@@ -5880,28 +5793,28 @@
       <c r="A46" s="45"/>
       <c r="B46" s="46"/>
       <c r="C46" s="99" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D46" s="14"/>
       <c r="E46" s="101" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F46" s="99" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G46" s="101">
         <v>0.09</v>
       </c>
       <c r="H46" s="14"/>
       <c r="I46" s="99" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J46" s="101">
         <v>0.089</v>
       </c>
       <c r="K46" s="14"/>
       <c r="L46" s="99" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M46" s="101">
         <v>0.09</v>
@@ -5909,28 +5822,28 @@
       <c r="N46" s="14"/>
       <c r="O46" s="52"/>
       <c r="P46" s="99" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Q46" s="14"/>
       <c r="R46" s="101" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="S46" s="99" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="T46" s="101">
         <v>0.09</v>
       </c>
       <c r="U46" s="14"/>
       <c r="V46" s="99" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="W46" s="101">
         <v>0.09</v>
       </c>
       <c r="X46" s="14"/>
       <c r="Y46" s="99" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="Z46" s="101">
         <v>0.093</v>
@@ -5945,7 +5858,7 @@
       <c r="A47" s="45"/>
       <c r="B47" s="46"/>
       <c r="C47" s="87" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D47" s="13"/>
       <c r="E47" s="13"/>
@@ -5960,7 +5873,7 @@
       <c r="N47" s="14"/>
       <c r="O47" s="52"/>
       <c r="P47" s="87" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Q47" s="13"/>
       <c r="R47" s="13"/>
@@ -5982,13 +5895,13 @@
       <c r="A48" s="45"/>
       <c r="B48" s="46"/>
       <c r="C48" s="99" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D48" s="101">
         <v>30.1</v>
       </c>
       <c r="E48" s="99" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F48" s="14"/>
       <c r="G48" s="101">
@@ -5996,7 +5909,7 @@
       </c>
       <c r="H48" s="14"/>
       <c r="I48" s="99" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J48" s="14"/>
       <c r="K48" s="101">
@@ -6004,7 +5917,7 @@
       </c>
       <c r="L48" s="14"/>
       <c r="M48" s="99" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="N48" s="101">
         <f>K48-G48</f>
@@ -6012,13 +5925,13 @@
       </c>
       <c r="O48" s="52"/>
       <c r="P48" s="99" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Q48" s="101">
         <v>30</v>
       </c>
       <c r="R48" s="99" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="S48" s="14"/>
       <c r="T48" s="101">
@@ -6026,7 +5939,7 @@
       </c>
       <c r="U48" s="14"/>
       <c r="V48" s="99" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="W48" s="14"/>
       <c r="X48" s="101">
@@ -6034,7 +5947,7 @@
       </c>
       <c r="Y48" s="14"/>
       <c r="Z48" s="99" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="AA48" s="99">
         <f>X48-T48</f>
@@ -6049,10 +5962,10 @@
       <c r="A49" s="62"/>
       <c r="B49" s="63"/>
       <c r="C49" s="99" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D49" s="87" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E49" s="13"/>
       <c r="F49" s="13"/>
@@ -6066,10 +5979,10 @@
       <c r="N49" s="14"/>
       <c r="O49" s="29"/>
       <c r="P49" s="99" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q49" s="87" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R49" s="13"/>
       <c r="S49" s="13"/>
@@ -6088,11 +6001,11 @@
     </row>
     <row r="50" spans="1:31">
       <c r="A50" s="25" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B50" s="14"/>
       <c r="C50" s="105" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D50" s="13"/>
       <c r="E50" s="13"/>
@@ -6125,11 +6038,11 @@
     </row>
     <row r="51" spans="1:31">
       <c r="A51" s="25" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B51" s="14"/>
       <c r="C51" s="105" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D51" s="13"/>
       <c r="E51" s="13"/>
@@ -6162,11 +6075,11 @@
     </row>
     <row r="52" spans="1:31">
       <c r="A52" s="25" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B52" s="14"/>
       <c r="C52" s="105" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D52" s="13"/>
       <c r="E52" s="13"/>
@@ -6199,11 +6112,11 @@
     </row>
     <row r="53" spans="1:31">
       <c r="A53" s="25" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B53" s="14"/>
       <c r="C53" s="105" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D53" s="13"/>
       <c r="E53" s="13"/>
@@ -6236,7 +6149,7 @@
     </row>
     <row r="54" spans="1:31">
       <c r="A54" s="106" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B54" s="13"/>
       <c r="C54" s="13"/>
@@ -6271,7 +6184,7 @@
     </row>
     <row r="55" ht="28" customHeight="1" spans="1:31">
       <c r="A55" s="107" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B55" s="108"/>
       <c r="C55" s="108"/>
@@ -6286,9 +6199,7 @@
       <c r="L55" s="108"/>
       <c r="M55" s="61"/>
       <c r="N55" s="61"/>
-      <c r="O55" s="109" t="s">
-        <v>142</v>
-      </c>
+      <c r="O55" s="109"/>
       <c r="P55" s="13"/>
       <c r="Q55" s="13"/>
       <c r="R55" s="13"/>
@@ -6302,61 +6213,61 @@
       <c r="Z55" s="14"/>
       <c r="AA55" s="61"/>
       <c r="AB55" s="110" t="s">
+        <v>141</v>
+      </c>
+      <c r="AC55" s="110" t="s">
+        <v>142</v>
+      </c>
+      <c r="AD55" s="111" t="s">
         <v>143</v>
-      </c>
-      <c r="AC55" s="110" t="s">
-        <v>144</v>
-      </c>
-      <c r="AD55" s="111" t="s">
-        <v>145</v>
       </c>
       <c r="AE55" s="14"/>
     </row>
     <row r="56" spans="1:31">
       <c r="A56" s="112" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B56" s="66"/>
       <c r="C56" s="113" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D56" s="66"/>
       <c r="E56" s="113" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F56" s="66"/>
       <c r="G56" s="114" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H56" s="66"/>
       <c r="I56" s="113" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="J56" s="66"/>
       <c r="K56" s="113" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="L56" s="66"/>
       <c r="M56" s="115"/>
       <c r="N56" s="115"/>
       <c r="O56" s="116" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="P56" s="13"/>
       <c r="Q56" s="14"/>
       <c r="R56" s="99" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="S56" s="13"/>
       <c r="T56" s="13"/>
       <c r="U56" s="14"/>
       <c r="V56" s="99" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="W56" s="13"/>
       <c r="X56" s="14"/>
       <c r="Y56" s="99" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="Z56" s="14"/>
       <c r="AA56" s="61"/>
@@ -6374,28 +6285,18 @@
     </row>
     <row r="57" spans="1:31">
       <c r="A57" s="112" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B57" s="66"/>
-      <c r="C57" s="113">
-        <v>112.91</v>
-      </c>
+      <c r="C57" s="113"/>
       <c r="D57" s="66"/>
-      <c r="E57" s="113">
-        <v>82.95</v>
-      </c>
+      <c r="E57" s="113"/>
       <c r="F57" s="66"/>
-      <c r="G57" s="113">
-        <v>16180</v>
-      </c>
+      <c r="G57" s="113"/>
       <c r="H57" s="66"/>
-      <c r="I57" s="113">
-        <v>0.99</v>
-      </c>
+      <c r="I57" s="113"/>
       <c r="J57" s="66"/>
-      <c r="K57" s="119">
-        <v>0.1634</v>
-      </c>
+      <c r="K57" s="119"/>
       <c r="L57" s="66"/>
       <c r="M57" s="61"/>
       <c r="N57" s="61"/>
@@ -6419,28 +6320,18 @@
     </row>
     <row r="58" spans="1:31">
       <c r="A58" s="112" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B58" s="66"/>
-      <c r="C58" s="113">
-        <v>114.75</v>
-      </c>
+      <c r="C58" s="113"/>
       <c r="D58" s="66"/>
-      <c r="E58" s="113">
-        <v>78.79</v>
-      </c>
+      <c r="E58" s="113"/>
       <c r="F58" s="66"/>
-      <c r="G58" s="113">
-        <v>15680</v>
-      </c>
+      <c r="G58" s="113"/>
       <c r="H58" s="66"/>
-      <c r="I58" s="113">
-        <v>0.99</v>
-      </c>
+      <c r="I58" s="113"/>
       <c r="J58" s="66"/>
-      <c r="K58" s="119">
-        <v>0.1584</v>
-      </c>
+      <c r="K58" s="119"/>
       <c r="L58" s="66"/>
       <c r="M58" s="61"/>
       <c r="N58" s="61"/>
@@ -6466,40 +6357,40 @@
       <c r="A59" s="127"/>
       <c r="B59" s="127"/>
       <c r="C59" s="112" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D59" s="66"/>
       <c r="E59" s="113" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F59" s="66"/>
       <c r="G59" s="114" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H59" s="66"/>
       <c r="I59" s="113" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="J59" s="66"/>
       <c r="K59" s="113" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="L59" s="66"/>
       <c r="M59" s="115"/>
       <c r="N59" s="115"/>
       <c r="O59" s="128" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="P59" s="13"/>
       <c r="Q59" s="13"/>
       <c r="R59" s="14"/>
       <c r="S59" s="99" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="T59" s="13"/>
       <c r="U59" s="14"/>
       <c r="V59" s="99" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="W59" s="13"/>
       <c r="X59" s="13"/>
@@ -6507,40 +6398,30 @@
       <c r="Z59" s="14"/>
       <c r="AA59" s="61"/>
       <c r="AB59" s="111" t="s">
+        <v>159</v>
+      </c>
+      <c r="AC59" s="111" t="s">
+        <v>160</v>
+      </c>
+      <c r="AD59" s="111" t="s">
         <v>161</v>
-      </c>
-      <c r="AC59" s="111" t="s">
-        <v>162</v>
-      </c>
-      <c r="AD59" s="111" t="s">
-        <v>163</v>
       </c>
       <c r="AE59" s="14"/>
     </row>
     <row r="60" spans="1:31">
       <c r="A60" s="112" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B60" s="66"/>
-      <c r="C60" s="113">
-        <v>10.18</v>
-      </c>
+      <c r="C60" s="113"/>
       <c r="D60" s="66"/>
-      <c r="E60" s="113">
-        <v>711.38</v>
-      </c>
+      <c r="E60" s="113"/>
       <c r="F60" s="66"/>
-      <c r="G60" s="113">
-        <v>12670</v>
-      </c>
+      <c r="G60" s="113"/>
       <c r="H60" s="66"/>
-      <c r="I60" s="113">
-        <v>1</v>
-      </c>
+      <c r="I60" s="113"/>
       <c r="J60" s="66"/>
-      <c r="K60" s="119">
-        <v>0.2534</v>
-      </c>
+      <c r="K60" s="119"/>
       <c r="L60" s="66"/>
       <c r="M60" s="61"/>
       <c r="N60" s="61"/>
@@ -6574,28 +6455,18 @@
     </row>
     <row r="61" spans="1:31">
       <c r="A61" s="112" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B61" s="66"/>
-      <c r="C61" s="113">
-        <v>10.21</v>
-      </c>
+      <c r="C61" s="113"/>
       <c r="D61" s="66"/>
-      <c r="E61" s="113">
-        <v>204.59</v>
-      </c>
+      <c r="E61" s="113"/>
       <c r="F61" s="66"/>
-      <c r="G61" s="113">
-        <v>3390</v>
-      </c>
+      <c r="G61" s="113"/>
       <c r="H61" s="66"/>
-      <c r="I61" s="113">
-        <v>0.96</v>
-      </c>
+      <c r="I61" s="113"/>
       <c r="J61" s="66"/>
-      <c r="K61" s="119">
-        <v>0.0706</v>
-      </c>
+      <c r="K61" s="119"/>
       <c r="L61" s="66"/>
       <c r="M61" s="61"/>
       <c r="N61" s="61"/>
@@ -6619,28 +6490,18 @@
     </row>
     <row r="62" spans="1:31">
       <c r="A62" s="112" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B62" s="66"/>
-      <c r="C62" s="113">
-        <v>10.25</v>
-      </c>
+      <c r="C62" s="113"/>
       <c r="D62" s="66"/>
-      <c r="E62" s="113">
-        <v>191.11</v>
-      </c>
+      <c r="E62" s="113"/>
       <c r="F62" s="66"/>
-      <c r="G62" s="113">
-        <v>3160</v>
-      </c>
+      <c r="G62" s="113"/>
       <c r="H62" s="66"/>
-      <c r="I62" s="113">
-        <v>0.96</v>
-      </c>
+      <c r="I62" s="113"/>
       <c r="J62" s="66"/>
-      <c r="K62" s="119">
-        <v>0.0658</v>
-      </c>
+      <c r="K62" s="119"/>
       <c r="L62" s="66"/>
       <c r="M62" s="130"/>
       <c r="N62" s="61"/>
@@ -6664,28 +6525,18 @@
     </row>
     <row r="63" spans="1:31">
       <c r="A63" s="112" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B63" s="66"/>
-      <c r="C63" s="113">
-        <v>10.23</v>
-      </c>
+      <c r="C63" s="113"/>
       <c r="D63" s="66"/>
-      <c r="E63" s="113">
-        <v>738.64</v>
-      </c>
+      <c r="E63" s="113"/>
       <c r="F63" s="66"/>
-      <c r="G63" s="113">
-        <v>13270</v>
-      </c>
+      <c r="G63" s="113"/>
       <c r="H63" s="66"/>
-      <c r="I63" s="113">
-        <v>1</v>
-      </c>
+      <c r="I63" s="113"/>
       <c r="J63" s="66"/>
-      <c r="K63" s="119">
-        <v>0.2654</v>
-      </c>
+      <c r="K63" s="119"/>
       <c r="L63" s="66"/>
       <c r="M63" s="130"/>
       <c r="N63" s="61"/>
@@ -6741,9 +6592,7 @@
       <c r="AE64" s="61"/>
     </row>
     <row r="65" ht="21" customHeight="1" spans="1:31">
-      <c r="A65" s="109" t="s">
-        <v>168</v>
-      </c>
+      <c r="A65" s="109"/>
       <c r="B65" s="13"/>
       <c r="C65" s="13"/>
       <c r="D65" s="13"/>
@@ -6777,104 +6626,104 @@
     </row>
     <row r="66" ht="24" customHeight="1" spans="1:31">
       <c r="A66" s="133" t="s">
+        <v>166</v>
+      </c>
+      <c r="B66" s="133" t="s">
+        <v>167</v>
+      </c>
+      <c r="C66" s="133" t="s">
+        <v>168</v>
+      </c>
+      <c r="D66" s="134" t="s">
         <v>169</v>
       </c>
-      <c r="B66" s="133" t="s">
+      <c r="E66" s="133" t="s">
         <v>170</v>
       </c>
-      <c r="C66" s="133" t="s">
+      <c r="F66" s="133" t="s">
         <v>171</v>
-      </c>
-      <c r="D66" s="134" t="s">
-        <v>172</v>
-      </c>
-      <c r="E66" s="133" t="s">
-        <v>173</v>
-      </c>
-      <c r="F66" s="133" t="s">
-        <v>174</v>
       </c>
       <c r="G66" s="14"/>
       <c r="H66" s="133" t="s">
+        <v>172</v>
+      </c>
+      <c r="I66" s="133" t="s">
+        <v>173</v>
+      </c>
+      <c r="J66" s="133" t="s">
+        <v>174</v>
+      </c>
+      <c r="K66" s="133" t="s">
+        <v>171</v>
+      </c>
+      <c r="L66" s="133" t="s">
         <v>175</v>
       </c>
-      <c r="I66" s="133" t="s">
+      <c r="M66" s="133" t="s">
         <v>176</v>
       </c>
-      <c r="J66" s="133" t="s">
+      <c r="N66" s="133" t="s">
         <v>177</v>
       </c>
-      <c r="K66" s="133" t="s">
-        <v>174</v>
-      </c>
-      <c r="L66" s="133" t="s">
+      <c r="O66" s="133" t="s">
         <v>178</v>
       </c>
-      <c r="M66" s="133" t="s">
+      <c r="P66" s="133" t="s">
         <v>179</v>
       </c>
-      <c r="N66" s="133" t="s">
+      <c r="Q66" s="133" t="s">
+        <v>177</v>
+      </c>
+      <c r="R66" s="133" t="s">
         <v>180</v>
       </c>
-      <c r="O66" s="133" t="s">
+      <c r="S66" s="133" t="s">
         <v>181</v>
-      </c>
-      <c r="P66" s="133" t="s">
-        <v>182</v>
-      </c>
-      <c r="Q66" s="133" t="s">
-        <v>180</v>
-      </c>
-      <c r="R66" s="133" t="s">
-        <v>183</v>
-      </c>
-      <c r="S66" s="133" t="s">
-        <v>184</v>
       </c>
       <c r="T66" s="14"/>
       <c r="U66" s="133" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="V66" s="133" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="W66" s="133" t="s">
+        <v>182</v>
+      </c>
+      <c r="X66" s="133" t="s">
+        <v>183</v>
+      </c>
+      <c r="Y66" s="133" t="s">
+        <v>184</v>
+      </c>
+      <c r="Z66" s="133" t="s">
         <v>185</v>
       </c>
-      <c r="X66" s="133" t="s">
+      <c r="AA66" s="133" t="s">
         <v>186</v>
       </c>
-      <c r="Y66" s="133" t="s">
+      <c r="AB66" s="133" t="s">
         <v>187</v>
       </c>
-      <c r="Z66" s="133" t="s">
+      <c r="AC66" s="133" t="s">
         <v>188</v>
       </c>
-      <c r="AA66" s="133" t="s">
+      <c r="AD66" s="133" t="s">
         <v>189</v>
       </c>
-      <c r="AB66" s="133" t="s">
+      <c r="AE66" s="133" t="s">
         <v>190</v>
-      </c>
-      <c r="AC66" s="133" t="s">
-        <v>191</v>
-      </c>
-      <c r="AD66" s="133" t="s">
-        <v>192</v>
-      </c>
-      <c r="AE66" s="133" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="67" spans="1:31">
       <c r="A67" s="135" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B67" s="136" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C67" s="135" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D67" s="137"/>
       <c r="E67" s="135"/>
@@ -6884,10 +6733,10 @@
       </c>
       <c r="G67" s="91"/>
       <c r="H67" s="139" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="I67" s="140" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="J67" s="135"/>
       <c r="K67" s="141">
@@ -6895,18 +6744,18 @@
         <v>0</v>
       </c>
       <c r="L67" s="135" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="M67" s="135"/>
       <c r="N67" s="135"/>
       <c r="O67" s="142" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="P67" s="143"/>
       <c r="Q67" s="143"/>
       <c r="R67" s="144"/>
       <c r="S67" s="145" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="T67" s="146"/>
       <c r="U67" s="147"/>
@@ -6939,7 +6788,7 @@
         <v>0</v>
       </c>
       <c r="AE67" s="135" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="68" spans="1:31">
@@ -6958,13 +6807,13 @@
       <c r="M68" s="52"/>
       <c r="N68" s="52"/>
       <c r="O68" s="142" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="P68" s="143"/>
       <c r="Q68" s="143"/>
       <c r="R68" s="144"/>
       <c r="S68" s="145" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="T68" s="146"/>
       <c r="U68" s="147"/>
@@ -6995,13 +6844,13 @@
       <c r="M69" s="52"/>
       <c r="N69" s="52"/>
       <c r="O69" s="142" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="P69" s="143"/>
       <c r="Q69" s="143"/>
       <c r="R69" s="144"/>
       <c r="S69" s="145" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="T69" s="146"/>
       <c r="U69" s="147"/>
@@ -7032,13 +6881,13 @@
       <c r="M70" s="52"/>
       <c r="N70" s="52"/>
       <c r="O70" s="142" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="P70" s="143"/>
       <c r="Q70" s="143"/>
       <c r="R70" s="144"/>
       <c r="S70" s="145" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="T70" s="146"/>
       <c r="U70" s="147"/>
@@ -7069,13 +6918,13 @@
       <c r="M71" s="52"/>
       <c r="N71" s="52"/>
       <c r="O71" s="142" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="P71" s="143"/>
       <c r="Q71" s="143"/>
       <c r="R71" s="144"/>
       <c r="S71" s="145" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="T71" s="146"/>
       <c r="U71" s="147"/>
@@ -7106,13 +6955,13 @@
       <c r="M72" s="52"/>
       <c r="N72" s="52"/>
       <c r="O72" s="142" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="P72" s="143"/>
       <c r="Q72" s="143"/>
       <c r="R72" s="144"/>
       <c r="S72" s="145" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="T72" s="146"/>
       <c r="U72" s="147"/>
@@ -7143,13 +6992,13 @@
       <c r="M73" s="52"/>
       <c r="N73" s="52"/>
       <c r="O73" s="142" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="P73" s="143"/>
       <c r="Q73" s="143"/>
       <c r="R73" s="144"/>
       <c r="S73" s="145" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="T73" s="146"/>
       <c r="U73" s="147"/>
@@ -7180,13 +7029,13 @@
       <c r="M74" s="52"/>
       <c r="N74" s="52"/>
       <c r="O74" s="142" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P74" s="143"/>
       <c r="Q74" s="143"/>
       <c r="R74" s="144"/>
       <c r="S74" s="145" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="T74" s="146"/>
       <c r="U74" s="147"/>
@@ -7217,13 +7066,13 @@
       <c r="M75" s="52"/>
       <c r="N75" s="52"/>
       <c r="O75" s="142" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="P75" s="143"/>
       <c r="Q75" s="143"/>
       <c r="R75" s="144"/>
       <c r="S75" s="145" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="T75" s="146"/>
       <c r="U75" s="147"/>
@@ -7254,13 +7103,13 @@
       <c r="M76" s="52"/>
       <c r="N76" s="52"/>
       <c r="O76" s="142" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="P76" s="143"/>
       <c r="Q76" s="143"/>
       <c r="R76" s="144"/>
       <c r="S76" s="145" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="T76" s="146"/>
       <c r="U76" s="147"/>
@@ -7278,10 +7127,10 @@
     <row r="77" spans="1:31">
       <c r="A77" s="52"/>
       <c r="B77" s="136" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C77" s="135" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D77" s="137"/>
       <c r="E77" s="135"/>
@@ -7291,7 +7140,7 @@
       </c>
       <c r="G77" s="91"/>
       <c r="H77" s="139" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="I77" s="148"/>
       <c r="J77" s="52"/>
@@ -7300,13 +7149,13 @@
       <c r="M77" s="52"/>
       <c r="N77" s="52"/>
       <c r="O77" s="142" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="P77" s="143"/>
       <c r="Q77" s="143"/>
       <c r="R77" s="144"/>
       <c r="S77" s="154" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="T77" s="146"/>
       <c r="U77" s="147"/>
@@ -7320,7 +7169,7 @@
       <c r="AC77" s="153"/>
       <c r="AD77" s="153"/>
       <c r="AE77" s="143" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="78" spans="1:31">
@@ -7339,13 +7188,13 @@
       <c r="M78" s="52"/>
       <c r="N78" s="52"/>
       <c r="O78" s="142" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="P78" s="143"/>
       <c r="Q78" s="143"/>
       <c r="R78" s="144"/>
       <c r="S78" s="154" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="T78" s="146"/>
       <c r="U78" s="147"/>
@@ -7376,13 +7225,13 @@
       <c r="M79" s="52"/>
       <c r="N79" s="52"/>
       <c r="O79" s="142" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="P79" s="143"/>
       <c r="Q79" s="143"/>
       <c r="R79" s="144"/>
       <c r="S79" s="154" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="T79" s="146"/>
       <c r="U79" s="147"/>
@@ -7413,13 +7262,13 @@
       <c r="M80" s="52"/>
       <c r="N80" s="52"/>
       <c r="O80" s="142" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="P80" s="143"/>
       <c r="Q80" s="143"/>
       <c r="R80" s="144"/>
       <c r="S80" s="154" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="T80" s="146"/>
       <c r="U80" s="147"/>
@@ -7450,13 +7299,13 @@
       <c r="M81" s="52"/>
       <c r="N81" s="52"/>
       <c r="O81" s="142" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="P81" s="143"/>
       <c r="Q81" s="143"/>
       <c r="R81" s="144"/>
       <c r="S81" s="154" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="T81" s="146"/>
       <c r="U81" s="147"/>
@@ -7487,13 +7336,13 @@
       <c r="M82" s="52"/>
       <c r="N82" s="52"/>
       <c r="O82" s="142" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="P82" s="143"/>
       <c r="Q82" s="143"/>
       <c r="R82" s="144"/>
       <c r="S82" s="154" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="T82" s="146"/>
       <c r="U82" s="147"/>
@@ -7524,13 +7373,13 @@
       <c r="M83" s="52"/>
       <c r="N83" s="52"/>
       <c r="O83" s="142" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="P83" s="143"/>
       <c r="Q83" s="143"/>
       <c r="R83" s="144"/>
       <c r="S83" s="154" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="T83" s="146"/>
       <c r="U83" s="147"/>
@@ -7561,13 +7410,13 @@
       <c r="M84" s="52"/>
       <c r="N84" s="52"/>
       <c r="O84" s="142" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="P84" s="143"/>
       <c r="Q84" s="143"/>
       <c r="R84" s="144"/>
       <c r="S84" s="154" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="T84" s="146"/>
       <c r="U84" s="147"/>
@@ -7598,13 +7447,13 @@
       <c r="M85" s="52"/>
       <c r="N85" s="52"/>
       <c r="O85" s="142" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="P85" s="143"/>
       <c r="Q85" s="143"/>
       <c r="R85" s="144"/>
       <c r="S85" s="154" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="T85" s="146"/>
       <c r="U85" s="147"/>
@@ -7635,13 +7484,13 @@
       <c r="M86" s="52"/>
       <c r="N86" s="52"/>
       <c r="O86" s="142" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="P86" s="143"/>
       <c r="Q86" s="143"/>
       <c r="R86" s="144"/>
       <c r="S86" s="154" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="T86" s="146"/>
       <c r="U86" s="147"/>
@@ -7658,13 +7507,13 @@
     </row>
     <row r="87" spans="1:31">
       <c r="A87" s="135" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B87" s="136" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C87" s="135" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D87" s="137"/>
       <c r="E87" s="135"/>
@@ -7674,10 +7523,10 @@
       </c>
       <c r="G87" s="91"/>
       <c r="H87" s="139" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="I87" s="155" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="J87" s="135"/>
       <c r="K87" s="141">
@@ -7685,18 +7534,18 @@
         <v>0</v>
       </c>
       <c r="L87" s="135" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="M87" s="135"/>
       <c r="N87" s="135"/>
       <c r="O87" s="142" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="P87" s="143"/>
       <c r="Q87" s="143"/>
       <c r="R87" s="144"/>
       <c r="S87" s="145" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="T87" s="146"/>
       <c r="U87" s="147"/>
@@ -7729,7 +7578,7 @@
         <v>0</v>
       </c>
       <c r="AE87" s="135" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="88" spans="1:31">
@@ -7748,13 +7597,13 @@
       <c r="M88" s="52"/>
       <c r="N88" s="52"/>
       <c r="O88" s="142" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="P88" s="143"/>
       <c r="Q88" s="143"/>
       <c r="R88" s="144"/>
       <c r="S88" s="145" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="T88" s="146"/>
       <c r="U88" s="147"/>
@@ -7785,13 +7634,13 @@
       <c r="M89" s="52"/>
       <c r="N89" s="52"/>
       <c r="O89" s="142" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="P89" s="143"/>
       <c r="Q89" s="143"/>
       <c r="R89" s="144"/>
       <c r="S89" s="145" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="T89" s="146"/>
       <c r="U89" s="147"/>
@@ -7822,13 +7671,13 @@
       <c r="M90" s="52"/>
       <c r="N90" s="52"/>
       <c r="O90" s="142" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="P90" s="143"/>
       <c r="Q90" s="143"/>
       <c r="R90" s="144"/>
       <c r="S90" s="145" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="T90" s="146"/>
       <c r="U90" s="147"/>
@@ -7859,13 +7708,13 @@
       <c r="M91" s="52"/>
       <c r="N91" s="52"/>
       <c r="O91" s="142" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="P91" s="143"/>
       <c r="Q91" s="143"/>
       <c r="R91" s="144"/>
       <c r="S91" s="145" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="T91" s="146"/>
       <c r="U91" s="147"/>
@@ -7896,13 +7745,13 @@
       <c r="M92" s="52"/>
       <c r="N92" s="52"/>
       <c r="O92" s="142" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="P92" s="143"/>
       <c r="Q92" s="143"/>
       <c r="R92" s="144"/>
       <c r="S92" s="145" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="T92" s="146"/>
       <c r="U92" s="147"/>
@@ -7933,13 +7782,13 @@
       <c r="M93" s="52"/>
       <c r="N93" s="52"/>
       <c r="O93" s="142" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="P93" s="143"/>
       <c r="Q93" s="143"/>
       <c r="R93" s="144"/>
       <c r="S93" s="145" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="T93" s="146"/>
       <c r="U93" s="147"/>
@@ -7970,13 +7819,13 @@
       <c r="M94" s="52"/>
       <c r="N94" s="52"/>
       <c r="O94" s="142" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="P94" s="143"/>
       <c r="Q94" s="143"/>
       <c r="R94" s="144"/>
       <c r="S94" s="145" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="T94" s="146"/>
       <c r="U94" s="147"/>
@@ -8007,13 +7856,13 @@
       <c r="M95" s="52"/>
       <c r="N95" s="52"/>
       <c r="O95" s="142" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="P95" s="143"/>
       <c r="Q95" s="143"/>
       <c r="R95" s="144"/>
       <c r="S95" s="145" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="T95" s="146"/>
       <c r="U95" s="147"/>
@@ -8044,13 +7893,13 @@
       <c r="M96" s="52"/>
       <c r="N96" s="52"/>
       <c r="O96" s="142" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="P96" s="143"/>
       <c r="Q96" s="143"/>
       <c r="R96" s="144"/>
       <c r="S96" s="145" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="T96" s="146"/>
       <c r="U96" s="147"/>
@@ -8068,10 +7917,10 @@
     <row r="97" spans="1:31">
       <c r="A97" s="52"/>
       <c r="B97" s="136" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C97" s="135" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D97" s="137"/>
       <c r="E97" s="135"/>
@@ -8081,7 +7930,7 @@
       </c>
       <c r="G97" s="91"/>
       <c r="H97" s="139" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="I97" s="148"/>
       <c r="J97" s="52"/>
@@ -8090,13 +7939,13 @@
       <c r="M97" s="52"/>
       <c r="N97" s="52"/>
       <c r="O97" s="142" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="P97" s="143"/>
       <c r="Q97" s="143"/>
       <c r="R97" s="144"/>
       <c r="S97" s="154" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="T97" s="146"/>
       <c r="U97" s="147"/>
@@ -8110,7 +7959,7 @@
       <c r="AC97" s="153"/>
       <c r="AD97" s="153"/>
       <c r="AE97" s="143" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="98" spans="1:31">
@@ -8129,13 +7978,13 @@
       <c r="M98" s="52"/>
       <c r="N98" s="52"/>
       <c r="O98" s="142" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="P98" s="143"/>
       <c r="Q98" s="143"/>
       <c r="R98" s="144"/>
       <c r="S98" s="154" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="T98" s="146"/>
       <c r="U98" s="147"/>
@@ -8166,13 +8015,13 @@
       <c r="M99" s="52"/>
       <c r="N99" s="52"/>
       <c r="O99" s="142" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="P99" s="143"/>
       <c r="Q99" s="143"/>
       <c r="R99" s="144"/>
       <c r="S99" s="154" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="T99" s="146"/>
       <c r="U99" s="147"/>
@@ -8203,13 +8052,13 @@
       <c r="M100" s="52"/>
       <c r="N100" s="52"/>
       <c r="O100" s="142" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="P100" s="143"/>
       <c r="Q100" s="143"/>
       <c r="R100" s="144"/>
       <c r="S100" s="154" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="T100" s="146"/>
       <c r="U100" s="147"/>
@@ -8240,13 +8089,13 @@
       <c r="M101" s="52"/>
       <c r="N101" s="52"/>
       <c r="O101" s="142" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="P101" s="143"/>
       <c r="Q101" s="143"/>
       <c r="R101" s="144"/>
       <c r="S101" s="154" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="T101" s="146"/>
       <c r="U101" s="147"/>
@@ -8277,13 +8126,13 @@
       <c r="M102" s="52"/>
       <c r="N102" s="52"/>
       <c r="O102" s="142" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="P102" s="143"/>
       <c r="Q102" s="143"/>
       <c r="R102" s="144"/>
       <c r="S102" s="154" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="T102" s="146"/>
       <c r="U102" s="147"/>
@@ -8314,13 +8163,13 @@
       <c r="M103" s="52"/>
       <c r="N103" s="52"/>
       <c r="O103" s="142" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="P103" s="143"/>
       <c r="Q103" s="143"/>
       <c r="R103" s="144"/>
       <c r="S103" s="154" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="T103" s="146"/>
       <c r="U103" s="147"/>
@@ -8351,13 +8200,13 @@
       <c r="M104" s="52"/>
       <c r="N104" s="52"/>
       <c r="O104" s="142" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="P104" s="143"/>
       <c r="Q104" s="143"/>
       <c r="R104" s="144"/>
       <c r="S104" s="154" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="T104" s="146"/>
       <c r="U104" s="147"/>
@@ -8388,13 +8237,13 @@
       <c r="M105" s="52"/>
       <c r="N105" s="52"/>
       <c r="O105" s="142" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="P105" s="143"/>
       <c r="Q105" s="143"/>
       <c r="R105" s="144"/>
       <c r="S105" s="154" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="T105" s="146"/>
       <c r="U105" s="147"/>
@@ -8425,13 +8274,13 @@
       <c r="M106" s="52"/>
       <c r="N106" s="52"/>
       <c r="O106" s="142" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="P106" s="143"/>
       <c r="Q106" s="143"/>
       <c r="R106" s="144"/>
       <c r="S106" s="154" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="T106" s="146"/>
       <c r="U106" s="147"/>
@@ -8448,13 +8297,13 @@
     </row>
     <row r="107" spans="1:31">
       <c r="A107" s="135" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B107" s="156" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="C107" s="143" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D107" s="137"/>
       <c r="E107" s="135"/>
@@ -8464,10 +8313,10 @@
       </c>
       <c r="G107" s="91"/>
       <c r="H107" s="117" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="I107" s="140" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="J107" s="135"/>
       <c r="K107" s="141">
@@ -8475,18 +8324,18 @@
         <v>0</v>
       </c>
       <c r="L107" s="135" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="M107" s="135"/>
       <c r="N107" s="135"/>
       <c r="O107" s="142" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="P107" s="143"/>
       <c r="Q107" s="143"/>
       <c r="R107" s="144"/>
       <c r="S107" s="145" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="T107" s="146"/>
       <c r="U107" s="147"/>
@@ -8519,7 +8368,7 @@
         <v>0</v>
       </c>
       <c r="AE107" s="135" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="108" spans="1:31">
@@ -8538,13 +8387,13 @@
       <c r="M108" s="52"/>
       <c r="N108" s="52"/>
       <c r="O108" s="142" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="P108" s="143"/>
       <c r="Q108" s="143"/>
       <c r="R108" s="144"/>
       <c r="S108" s="145" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="T108" s="146"/>
       <c r="U108" s="147"/>
@@ -8575,13 +8424,13 @@
       <c r="M109" s="52"/>
       <c r="N109" s="52"/>
       <c r="O109" s="142" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="P109" s="143"/>
       <c r="Q109" s="143"/>
       <c r="R109" s="144"/>
       <c r="S109" s="145" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="T109" s="146"/>
       <c r="U109" s="147"/>
@@ -8612,13 +8461,13 @@
       <c r="M110" s="52"/>
       <c r="N110" s="52"/>
       <c r="O110" s="142" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="P110" s="143"/>
       <c r="Q110" s="143"/>
       <c r="R110" s="144"/>
       <c r="S110" s="145" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="T110" s="146"/>
       <c r="U110" s="147"/>
@@ -8649,13 +8498,13 @@
       <c r="M111" s="52"/>
       <c r="N111" s="52"/>
       <c r="O111" s="142" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="P111" s="143"/>
       <c r="Q111" s="143"/>
       <c r="R111" s="144"/>
       <c r="S111" s="145" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="T111" s="146"/>
       <c r="U111" s="147"/>
@@ -8686,13 +8535,13 @@
       <c r="M112" s="52"/>
       <c r="N112" s="52"/>
       <c r="O112" s="142" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="P112" s="143"/>
       <c r="Q112" s="143"/>
       <c r="R112" s="144"/>
       <c r="S112" s="145" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="T112" s="146"/>
       <c r="U112" s="147"/>
@@ -8723,13 +8572,13 @@
       <c r="M113" s="52"/>
       <c r="N113" s="52"/>
       <c r="O113" s="142" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="P113" s="143"/>
       <c r="Q113" s="143"/>
       <c r="R113" s="144"/>
       <c r="S113" s="145" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="T113" s="146"/>
       <c r="U113" s="147"/>
@@ -8760,13 +8609,13 @@
       <c r="M114" s="52"/>
       <c r="N114" s="52"/>
       <c r="O114" s="142" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="P114" s="143"/>
       <c r="Q114" s="143"/>
       <c r="R114" s="144"/>
       <c r="S114" s="145" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="T114" s="146"/>
       <c r="U114" s="147"/>
@@ -8797,13 +8646,13 @@
       <c r="M115" s="52"/>
       <c r="N115" s="52"/>
       <c r="O115" s="142" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="P115" s="143"/>
       <c r="Q115" s="143"/>
       <c r="R115" s="144"/>
       <c r="S115" s="145" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="T115" s="146"/>
       <c r="U115" s="147"/>
@@ -8834,13 +8683,13 @@
       <c r="M116" s="52"/>
       <c r="N116" s="52"/>
       <c r="O116" s="142" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="P116" s="143"/>
       <c r="Q116" s="143"/>
       <c r="R116" s="144"/>
       <c r="S116" s="145" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="T116" s="146"/>
       <c r="U116" s="147"/>
@@ -8858,10 +8707,10 @@
     <row r="117" spans="1:31">
       <c r="A117" s="52"/>
       <c r="B117" s="156" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="C117" s="143" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D117" s="137"/>
       <c r="E117" s="135"/>
@@ -8871,7 +8720,7 @@
       </c>
       <c r="G117" s="91"/>
       <c r="H117" s="117" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="I117" s="148"/>
       <c r="J117" s="52"/>
@@ -8880,13 +8729,13 @@
       <c r="M117" s="52"/>
       <c r="N117" s="52"/>
       <c r="O117" s="142" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="P117" s="143"/>
       <c r="Q117" s="143"/>
       <c r="R117" s="144"/>
       <c r="S117" s="154" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="T117" s="146"/>
       <c r="U117" s="147"/>
@@ -8900,7 +8749,7 @@
       <c r="AC117" s="153"/>
       <c r="AD117" s="153"/>
       <c r="AE117" s="143" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="118" spans="1:31">
@@ -8919,13 +8768,13 @@
       <c r="M118" s="52"/>
       <c r="N118" s="52"/>
       <c r="O118" s="142" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="P118" s="143"/>
       <c r="Q118" s="143"/>
       <c r="R118" s="144"/>
       <c r="S118" s="154" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="T118" s="146"/>
       <c r="U118" s="147"/>
@@ -8956,13 +8805,13 @@
       <c r="M119" s="52"/>
       <c r="N119" s="52"/>
       <c r="O119" s="142" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="P119" s="143"/>
       <c r="Q119" s="143"/>
       <c r="R119" s="144"/>
       <c r="S119" s="154" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="T119" s="146"/>
       <c r="U119" s="147"/>
@@ -8993,13 +8842,13 @@
       <c r="M120" s="52"/>
       <c r="N120" s="52"/>
       <c r="O120" s="142" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="P120" s="143"/>
       <c r="Q120" s="143"/>
       <c r="R120" s="144"/>
       <c r="S120" s="154" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="T120" s="146"/>
       <c r="U120" s="147"/>
@@ -9030,13 +8879,13 @@
       <c r="M121" s="52"/>
       <c r="N121" s="52"/>
       <c r="O121" s="142" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="P121" s="143"/>
       <c r="Q121" s="143"/>
       <c r="R121" s="144"/>
       <c r="S121" s="154" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="T121" s="146"/>
       <c r="U121" s="147"/>
@@ -9067,13 +8916,13 @@
       <c r="M122" s="52"/>
       <c r="N122" s="52"/>
       <c r="O122" s="142" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="P122" s="143"/>
       <c r="Q122" s="143"/>
       <c r="R122" s="144"/>
       <c r="S122" s="154" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="T122" s="146"/>
       <c r="U122" s="147"/>
@@ -9104,13 +8953,13 @@
       <c r="M123" s="52"/>
       <c r="N123" s="52"/>
       <c r="O123" s="142" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="P123" s="143"/>
       <c r="Q123" s="143"/>
       <c r="R123" s="144"/>
       <c r="S123" s="154" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="T123" s="146"/>
       <c r="U123" s="147"/>
@@ -9141,13 +8990,13 @@
       <c r="M124" s="52"/>
       <c r="N124" s="52"/>
       <c r="O124" s="142" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="P124" s="143"/>
       <c r="Q124" s="143"/>
       <c r="R124" s="144"/>
       <c r="S124" s="154" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="T124" s="146"/>
       <c r="U124" s="147"/>
@@ -9178,13 +9027,13 @@
       <c r="M125" s="52"/>
       <c r="N125" s="52"/>
       <c r="O125" s="142" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="P125" s="143"/>
       <c r="Q125" s="143"/>
       <c r="R125" s="144"/>
       <c r="S125" s="154" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="T125" s="146"/>
       <c r="U125" s="147"/>
@@ -9215,13 +9064,13 @@
       <c r="M126" s="52"/>
       <c r="N126" s="52"/>
       <c r="O126" s="142" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="P126" s="143"/>
       <c r="Q126" s="143"/>
       <c r="R126" s="144"/>
       <c r="S126" s="154" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="T126" s="146"/>
       <c r="U126" s="147"/>
@@ -9238,13 +9087,13 @@
     </row>
     <row r="127" spans="1:31">
       <c r="A127" s="135" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="B127" s="156" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C127" s="143" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D127" s="137"/>
       <c r="E127" s="135"/>
@@ -9254,10 +9103,10 @@
       </c>
       <c r="G127" s="91"/>
       <c r="H127" s="117" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="I127" s="140" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="J127" s="135"/>
       <c r="K127" s="141">
@@ -9265,18 +9114,18 @@
         <v>0</v>
       </c>
       <c r="L127" s="135" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="M127" s="135"/>
       <c r="N127" s="135"/>
       <c r="O127" s="142" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="P127" s="143"/>
       <c r="Q127" s="143"/>
       <c r="R127" s="144"/>
       <c r="S127" s="145" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="T127" s="146"/>
       <c r="U127" s="147"/>
@@ -9309,7 +9158,7 @@
         <v>0</v>
       </c>
       <c r="AE127" s="135" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="128" spans="1:31">
@@ -9328,13 +9177,13 @@
       <c r="M128" s="52"/>
       <c r="N128" s="52"/>
       <c r="O128" s="142" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="P128" s="143"/>
       <c r="Q128" s="143"/>
       <c r="R128" s="144"/>
       <c r="S128" s="145" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="T128" s="146"/>
       <c r="U128" s="147"/>
@@ -9365,13 +9214,13 @@
       <c r="M129" s="52"/>
       <c r="N129" s="52"/>
       <c r="O129" s="142" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="P129" s="143"/>
       <c r="Q129" s="143"/>
       <c r="R129" s="144"/>
       <c r="S129" s="145" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="T129" s="146"/>
       <c r="U129" s="147"/>
@@ -9402,13 +9251,13 @@
       <c r="M130" s="52"/>
       <c r="N130" s="52"/>
       <c r="O130" s="142" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="P130" s="143"/>
       <c r="Q130" s="143"/>
       <c r="R130" s="144"/>
       <c r="S130" s="145" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="T130" s="146"/>
       <c r="U130" s="147"/>
@@ -9439,13 +9288,13 @@
       <c r="M131" s="52"/>
       <c r="N131" s="52"/>
       <c r="O131" s="142" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="P131" s="143"/>
       <c r="Q131" s="143"/>
       <c r="R131" s="144"/>
       <c r="S131" s="145" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="T131" s="146"/>
       <c r="U131" s="147"/>
@@ -9476,13 +9325,13 @@
       <c r="M132" s="52"/>
       <c r="N132" s="52"/>
       <c r="O132" s="142" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="P132" s="143"/>
       <c r="Q132" s="143"/>
       <c r="R132" s="144"/>
       <c r="S132" s="145" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="T132" s="146"/>
       <c r="U132" s="147"/>
@@ -9513,13 +9362,13 @@
       <c r="M133" s="52"/>
       <c r="N133" s="52"/>
       <c r="O133" s="142" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="P133" s="143"/>
       <c r="Q133" s="143"/>
       <c r="R133" s="144"/>
       <c r="S133" s="145" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="T133" s="146"/>
       <c r="U133" s="147"/>
@@ -9550,13 +9399,13 @@
       <c r="M134" s="52"/>
       <c r="N134" s="52"/>
       <c r="O134" s="142" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="P134" s="143"/>
       <c r="Q134" s="143"/>
       <c r="R134" s="144"/>
       <c r="S134" s="145" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="T134" s="146"/>
       <c r="U134" s="147"/>
@@ -9587,13 +9436,13 @@
       <c r="M135" s="52"/>
       <c r="N135" s="52"/>
       <c r="O135" s="142" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="P135" s="143"/>
       <c r="Q135" s="143"/>
       <c r="R135" s="144"/>
       <c r="S135" s="145" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="T135" s="146"/>
       <c r="U135" s="147"/>
@@ -9624,13 +9473,13 @@
       <c r="M136" s="52"/>
       <c r="N136" s="52"/>
       <c r="O136" s="142" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="P136" s="143"/>
       <c r="Q136" s="143"/>
       <c r="R136" s="144"/>
       <c r="S136" s="145" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="T136" s="146"/>
       <c r="U136" s="147"/>
@@ -9648,10 +9497,10 @@
     <row r="137" spans="1:31">
       <c r="A137" s="52"/>
       <c r="B137" s="156" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C137" s="143" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D137" s="137"/>
       <c r="E137" s="135"/>
@@ -9661,7 +9510,7 @@
       </c>
       <c r="G137" s="91"/>
       <c r="H137" s="117" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="I137" s="148"/>
       <c r="J137" s="52"/>
@@ -9670,13 +9519,13 @@
       <c r="M137" s="52"/>
       <c r="N137" s="52"/>
       <c r="O137" s="142" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="P137" s="143"/>
       <c r="Q137" s="143"/>
       <c r="R137" s="144"/>
       <c r="S137" s="154" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="T137" s="146"/>
       <c r="U137" s="147"/>
@@ -9690,7 +9539,7 @@
       <c r="AC137" s="153"/>
       <c r="AD137" s="153"/>
       <c r="AE137" s="143" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="138" spans="1:31">
@@ -9709,13 +9558,13 @@
       <c r="M138" s="52"/>
       <c r="N138" s="52"/>
       <c r="O138" s="142" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="P138" s="143"/>
       <c r="Q138" s="143"/>
       <c r="R138" s="144"/>
       <c r="S138" s="154" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="T138" s="146"/>
       <c r="U138" s="147"/>
@@ -9746,13 +9595,13 @@
       <c r="M139" s="52"/>
       <c r="N139" s="52"/>
       <c r="O139" s="142" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="P139" s="143"/>
       <c r="Q139" s="143"/>
       <c r="R139" s="144"/>
       <c r="S139" s="154" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="T139" s="146"/>
       <c r="U139" s="147"/>
@@ -9783,13 +9632,13 @@
       <c r="M140" s="52"/>
       <c r="N140" s="52"/>
       <c r="O140" s="142" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="P140" s="143"/>
       <c r="Q140" s="143"/>
       <c r="R140" s="144"/>
       <c r="S140" s="154" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="T140" s="146"/>
       <c r="U140" s="147"/>
@@ -9820,13 +9669,13 @@
       <c r="M141" s="52"/>
       <c r="N141" s="52"/>
       <c r="O141" s="142" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="P141" s="143"/>
       <c r="Q141" s="143"/>
       <c r="R141" s="144"/>
       <c r="S141" s="154" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="T141" s="146"/>
       <c r="U141" s="147"/>
@@ -9857,13 +9706,13 @@
       <c r="M142" s="52"/>
       <c r="N142" s="52"/>
       <c r="O142" s="142" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="P142" s="143"/>
       <c r="Q142" s="143"/>
       <c r="R142" s="144"/>
       <c r="S142" s="154" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="T142" s="146"/>
       <c r="U142" s="147"/>
@@ -9894,13 +9743,13 @@
       <c r="M143" s="52"/>
       <c r="N143" s="52"/>
       <c r="O143" s="142" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="P143" s="143"/>
       <c r="Q143" s="143"/>
       <c r="R143" s="144"/>
       <c r="S143" s="154" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="T143" s="146"/>
       <c r="U143" s="147"/>
@@ -9931,13 +9780,13 @@
       <c r="M144" s="52"/>
       <c r="N144" s="52"/>
       <c r="O144" s="142" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="P144" s="143"/>
       <c r="Q144" s="143"/>
       <c r="R144" s="144"/>
       <c r="S144" s="154" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="T144" s="146"/>
       <c r="U144" s="147"/>
@@ -9968,13 +9817,13 @@
       <c r="M145" s="52"/>
       <c r="N145" s="52"/>
       <c r="O145" s="142" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="P145" s="143"/>
       <c r="Q145" s="143"/>
       <c r="R145" s="144"/>
       <c r="S145" s="154" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="T145" s="146"/>
       <c r="U145" s="147"/>
@@ -10005,13 +9854,13 @@
       <c r="M146" s="52"/>
       <c r="N146" s="52"/>
       <c r="O146" s="142" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="P146" s="143"/>
       <c r="Q146" s="143"/>
       <c r="R146" s="144"/>
       <c r="S146" s="154" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="T146" s="146"/>
       <c r="U146" s="147"/>
@@ -10028,13 +9877,13 @@
     </row>
     <row r="147" spans="1:31">
       <c r="A147" s="135" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B147" s="136" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="C147" s="135" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D147" s="137"/>
       <c r="E147" s="135"/>
@@ -10044,10 +9893,10 @@
       </c>
       <c r="G147" s="91"/>
       <c r="H147" s="139" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="I147" s="158" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="J147" s="135"/>
       <c r="K147" s="141">
@@ -10055,18 +9904,18 @@
         <v>0</v>
       </c>
       <c r="L147" s="135" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="M147" s="135"/>
       <c r="N147" s="135"/>
       <c r="O147" s="142" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="P147" s="143"/>
       <c r="Q147" s="143"/>
       <c r="R147" s="144"/>
       <c r="S147" s="145" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="T147" s="146"/>
       <c r="U147" s="147"/>
@@ -10099,7 +9948,7 @@
         <v>14</v>
       </c>
       <c r="AE147" s="135" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="148" spans="1:31">
@@ -10118,13 +9967,13 @@
       <c r="M148" s="52"/>
       <c r="N148" s="52"/>
       <c r="O148" s="142" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="P148" s="143"/>
       <c r="Q148" s="143"/>
       <c r="R148" s="144"/>
       <c r="S148" s="145" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="T148" s="146"/>
       <c r="U148" s="147"/>
@@ -10155,13 +10004,13 @@
       <c r="M149" s="52"/>
       <c r="N149" s="52"/>
       <c r="O149" s="142" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="P149" s="143"/>
       <c r="Q149" s="143"/>
       <c r="R149" s="144"/>
       <c r="S149" s="145" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="T149" s="146"/>
       <c r="U149" s="147"/>
@@ -10192,13 +10041,13 @@
       <c r="M150" s="52"/>
       <c r="N150" s="52"/>
       <c r="O150" s="142" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="P150" s="143"/>
       <c r="Q150" s="143"/>
       <c r="R150" s="144"/>
       <c r="S150" s="145" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="T150" s="146"/>
       <c r="U150" s="147"/>
@@ -10229,13 +10078,13 @@
       <c r="M151" s="52"/>
       <c r="N151" s="52"/>
       <c r="O151" s="142" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="P151" s="143"/>
       <c r="Q151" s="143"/>
       <c r="R151" s="144"/>
       <c r="S151" s="145" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="T151" s="146"/>
       <c r="U151" s="147"/>
@@ -10266,13 +10115,13 @@
       <c r="M152" s="52"/>
       <c r="N152" s="52"/>
       <c r="O152" s="142" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="P152" s="143"/>
       <c r="Q152" s="143"/>
       <c r="R152" s="144"/>
       <c r="S152" s="145" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="T152" s="146"/>
       <c r="U152" s="147"/>
@@ -10303,13 +10152,13 @@
       <c r="M153" s="52"/>
       <c r="N153" s="52"/>
       <c r="O153" s="142" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="P153" s="143"/>
       <c r="Q153" s="143"/>
       <c r="R153" s="144"/>
       <c r="S153" s="145" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="T153" s="146"/>
       <c r="U153" s="147"/>
@@ -10340,13 +10189,13 @@
       <c r="M154" s="52"/>
       <c r="N154" s="52"/>
       <c r="O154" s="142" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="P154" s="143"/>
       <c r="Q154" s="143"/>
       <c r="R154" s="144"/>
       <c r="S154" s="145" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="T154" s="146"/>
       <c r="U154" s="147"/>
@@ -10377,13 +10226,13 @@
       <c r="M155" s="52"/>
       <c r="N155" s="52"/>
       <c r="O155" s="142" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="P155" s="143"/>
       <c r="Q155" s="143"/>
       <c r="R155" s="144"/>
       <c r="S155" s="145" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="T155" s="146"/>
       <c r="U155" s="147"/>
@@ -10414,13 +10263,13 @@
       <c r="M156" s="52"/>
       <c r="N156" s="52"/>
       <c r="O156" s="142" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="P156" s="143"/>
       <c r="Q156" s="143"/>
       <c r="R156" s="144"/>
       <c r="S156" s="145" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="T156" s="146"/>
       <c r="U156" s="147"/>
@@ -10438,10 +10287,10 @@
     <row r="157" spans="1:31">
       <c r="A157" s="52"/>
       <c r="B157" s="136" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="C157" s="135" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D157" s="137"/>
       <c r="E157" s="135"/>
@@ -10451,7 +10300,7 @@
       </c>
       <c r="G157" s="91"/>
       <c r="H157" s="139" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="I157" s="148"/>
       <c r="J157" s="52"/>
@@ -10460,13 +10309,13 @@
       <c r="M157" s="52"/>
       <c r="N157" s="52"/>
       <c r="O157" s="142" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="P157" s="143"/>
       <c r="Q157" s="143"/>
       <c r="R157" s="144"/>
       <c r="S157" s="154" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="T157" s="146"/>
       <c r="U157" s="147"/>
@@ -10480,7 +10329,7 @@
       <c r="AC157" s="153"/>
       <c r="AD157" s="153"/>
       <c r="AE157" s="143" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="158" spans="1:31">
@@ -10499,13 +10348,13 @@
       <c r="M158" s="52"/>
       <c r="N158" s="52"/>
       <c r="O158" s="142" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="P158" s="143"/>
       <c r="Q158" s="143"/>
       <c r="R158" s="144"/>
       <c r="S158" s="154" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="T158" s="146"/>
       <c r="U158" s="147"/>
@@ -10536,13 +10385,13 @@
       <c r="M159" s="52"/>
       <c r="N159" s="52"/>
       <c r="O159" s="142" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="P159" s="143"/>
       <c r="Q159" s="143"/>
       <c r="R159" s="144"/>
       <c r="S159" s="154" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="T159" s="146"/>
       <c r="U159" s="147"/>
@@ -10573,13 +10422,13 @@
       <c r="M160" s="52"/>
       <c r="N160" s="52"/>
       <c r="O160" s="142" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="P160" s="143"/>
       <c r="Q160" s="143"/>
       <c r="R160" s="144"/>
       <c r="S160" s="154" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="T160" s="146"/>
       <c r="U160" s="147"/>
@@ -10610,13 +10459,13 @@
       <c r="M161" s="52"/>
       <c r="N161" s="52"/>
       <c r="O161" s="142" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="P161" s="143"/>
       <c r="Q161" s="143"/>
       <c r="R161" s="144"/>
       <c r="S161" s="154" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="T161" s="146"/>
       <c r="U161" s="147"/>
@@ -10647,13 +10496,13 @@
       <c r="M162" s="52"/>
       <c r="N162" s="52"/>
       <c r="O162" s="142" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="P162" s="143"/>
       <c r="Q162" s="143"/>
       <c r="R162" s="144"/>
       <c r="S162" s="154" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="T162" s="146"/>
       <c r="U162" s="147"/>
@@ -10684,13 +10533,13 @@
       <c r="M163" s="52"/>
       <c r="N163" s="52"/>
       <c r="O163" s="142" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="P163" s="143"/>
       <c r="Q163" s="143"/>
       <c r="R163" s="144"/>
       <c r="S163" s="154" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="T163" s="146"/>
       <c r="U163" s="147"/>
@@ -10721,13 +10570,13 @@
       <c r="M164" s="52"/>
       <c r="N164" s="52"/>
       <c r="O164" s="142" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="P164" s="143"/>
       <c r="Q164" s="143"/>
       <c r="R164" s="144"/>
       <c r="S164" s="154" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="T164" s="146"/>
       <c r="U164" s="147"/>
@@ -10758,13 +10607,13 @@
       <c r="M165" s="52"/>
       <c r="N165" s="52"/>
       <c r="O165" s="142" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="P165" s="143"/>
       <c r="Q165" s="143"/>
       <c r="R165" s="144"/>
       <c r="S165" s="154" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="T165" s="146"/>
       <c r="U165" s="147"/>
@@ -10795,13 +10644,13 @@
       <c r="M166" s="52"/>
       <c r="N166" s="52"/>
       <c r="O166" s="159" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="P166" s="135"/>
       <c r="Q166" s="135"/>
       <c r="R166" s="160"/>
       <c r="S166" s="161" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="T166" s="162"/>
       <c r="U166" s="141"/>
@@ -10818,13 +10667,13 @@
     </row>
     <row r="167" spans="1:31">
       <c r="A167" s="135" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="B167" s="136" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="C167" s="135" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D167" s="137"/>
       <c r="E167" s="135"/>
@@ -10834,10 +10683,10 @@
       </c>
       <c r="G167" s="91"/>
       <c r="H167" s="139" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="I167" s="158" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="J167" s="135"/>
       <c r="K167" s="141">
@@ -10845,18 +10694,18 @@
         <v>0</v>
       </c>
       <c r="L167" s="135" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="M167" s="135"/>
       <c r="N167" s="135"/>
       <c r="O167" s="142" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="P167" s="143"/>
       <c r="Q167" s="143"/>
       <c r="R167" s="163"/>
       <c r="S167" s="145" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="T167" s="146"/>
       <c r="U167" s="147"/>
@@ -10889,7 +10738,7 @@
         <v>12</v>
       </c>
       <c r="AE167" s="135" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="168" spans="1:31">
@@ -10908,13 +10757,13 @@
       <c r="M168" s="52"/>
       <c r="N168" s="52"/>
       <c r="O168" s="142" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="P168" s="143"/>
       <c r="Q168" s="143"/>
       <c r="R168" s="163"/>
       <c r="S168" s="145" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="T168" s="146"/>
       <c r="U168" s="147"/>
@@ -10945,13 +10794,13 @@
       <c r="M169" s="52"/>
       <c r="N169" s="52"/>
       <c r="O169" s="142" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="P169" s="143"/>
       <c r="Q169" s="143"/>
       <c r="R169" s="163"/>
       <c r="S169" s="145" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="T169" s="146"/>
       <c r="U169" s="147"/>
@@ -10982,13 +10831,13 @@
       <c r="M170" s="52"/>
       <c r="N170" s="52"/>
       <c r="O170" s="142" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="P170" s="143"/>
       <c r="Q170" s="143"/>
       <c r="R170" s="163"/>
       <c r="S170" s="145" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="T170" s="146"/>
       <c r="U170" s="147"/>
@@ -11019,13 +10868,13 @@
       <c r="M171" s="52"/>
       <c r="N171" s="52"/>
       <c r="O171" s="142" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="P171" s="143"/>
       <c r="Q171" s="143"/>
       <c r="R171" s="163"/>
       <c r="S171" s="145" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="T171" s="146"/>
       <c r="U171" s="147"/>
@@ -11056,13 +10905,13 @@
       <c r="M172" s="52"/>
       <c r="N172" s="52"/>
       <c r="O172" s="142" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="P172" s="143"/>
       <c r="Q172" s="143"/>
       <c r="R172" s="163"/>
       <c r="S172" s="145" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="T172" s="146"/>
       <c r="U172" s="147"/>
@@ -11093,13 +10942,13 @@
       <c r="M173" s="52"/>
       <c r="N173" s="52"/>
       <c r="O173" s="142" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="P173" s="143"/>
       <c r="Q173" s="143"/>
       <c r="R173" s="163"/>
       <c r="S173" s="145" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="T173" s="146"/>
       <c r="U173" s="147"/>
@@ -11130,13 +10979,13 @@
       <c r="M174" s="52"/>
       <c r="N174" s="52"/>
       <c r="O174" s="142" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="P174" s="143"/>
       <c r="Q174" s="143"/>
       <c r="R174" s="163"/>
       <c r="S174" s="145" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="T174" s="146"/>
       <c r="U174" s="147"/>
@@ -11167,13 +11016,13 @@
       <c r="M175" s="52"/>
       <c r="N175" s="52"/>
       <c r="O175" s="142" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="P175" s="143"/>
       <c r="Q175" s="143"/>
       <c r="R175" s="163"/>
       <c r="S175" s="145" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="T175" s="146"/>
       <c r="U175" s="147"/>
@@ -11204,13 +11053,13 @@
       <c r="M176" s="52"/>
       <c r="N176" s="52"/>
       <c r="O176" s="142" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="P176" s="143"/>
       <c r="Q176" s="143"/>
       <c r="R176" s="163"/>
       <c r="S176" s="145" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="T176" s="146"/>
       <c r="U176" s="147"/>
@@ -11228,10 +11077,10 @@
     <row r="177" spans="1:31">
       <c r="A177" s="52"/>
       <c r="B177" s="136" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="C177" s="135" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D177" s="137"/>
       <c r="E177" s="135"/>
@@ -11241,7 +11090,7 @@
       </c>
       <c r="G177" s="91"/>
       <c r="H177" s="139" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="I177" s="148"/>
       <c r="J177" s="52"/>
@@ -11250,13 +11099,13 @@
       <c r="M177" s="52"/>
       <c r="N177" s="52"/>
       <c r="O177" s="142" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="P177" s="143"/>
       <c r="Q177" s="143"/>
       <c r="R177" s="163"/>
       <c r="S177" s="154" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="T177" s="146"/>
       <c r="U177" s="147"/>
@@ -11270,7 +11119,7 @@
       <c r="AC177" s="143"/>
       <c r="AD177" s="143"/>
       <c r="AE177" s="143" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="178" spans="1:31">
@@ -11289,13 +11138,13 @@
       <c r="M178" s="52"/>
       <c r="N178" s="52"/>
       <c r="O178" s="142" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="P178" s="143"/>
       <c r="Q178" s="143"/>
       <c r="R178" s="163"/>
       <c r="S178" s="154" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="T178" s="146"/>
       <c r="U178" s="147"/>
@@ -11326,13 +11175,13 @@
       <c r="M179" s="52"/>
       <c r="N179" s="52"/>
       <c r="O179" s="142" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="P179" s="143"/>
       <c r="Q179" s="143"/>
       <c r="R179" s="163"/>
       <c r="S179" s="154" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="T179" s="146"/>
       <c r="U179" s="147"/>
@@ -11363,13 +11212,13 @@
       <c r="M180" s="52"/>
       <c r="N180" s="52"/>
       <c r="O180" s="142" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="P180" s="143"/>
       <c r="Q180" s="143"/>
       <c r="R180" s="163"/>
       <c r="S180" s="154" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="T180" s="146"/>
       <c r="U180" s="147"/>
@@ -11400,13 +11249,13 @@
       <c r="M181" s="52"/>
       <c r="N181" s="52"/>
       <c r="O181" s="142" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="P181" s="143"/>
       <c r="Q181" s="143"/>
       <c r="R181" s="163"/>
       <c r="S181" s="154" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="T181" s="146"/>
       <c r="U181" s="147"/>
@@ -11437,13 +11286,13 @@
       <c r="M182" s="52"/>
       <c r="N182" s="52"/>
       <c r="O182" s="142" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="P182" s="143"/>
       <c r="Q182" s="143"/>
       <c r="R182" s="163"/>
       <c r="S182" s="154" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="T182" s="146"/>
       <c r="U182" s="147"/>
@@ -11474,13 +11323,13 @@
       <c r="M183" s="52"/>
       <c r="N183" s="52"/>
       <c r="O183" s="142" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="P183" s="143"/>
       <c r="Q183" s="143"/>
       <c r="R183" s="163"/>
       <c r="S183" s="154" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="T183" s="146"/>
       <c r="U183" s="147"/>
@@ -11511,13 +11360,13 @@
       <c r="M184" s="52"/>
       <c r="N184" s="52"/>
       <c r="O184" s="142" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="P184" s="143"/>
       <c r="Q184" s="143"/>
       <c r="R184" s="163"/>
       <c r="S184" s="154" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="T184" s="146"/>
       <c r="U184" s="147"/>
@@ -11548,13 +11397,13 @@
       <c r="M185" s="52"/>
       <c r="N185" s="52"/>
       <c r="O185" s="142" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="P185" s="143"/>
       <c r="Q185" s="143"/>
       <c r="R185" s="163"/>
       <c r="S185" s="154" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="T185" s="146"/>
       <c r="U185" s="147"/>
@@ -11585,13 +11434,13 @@
       <c r="M186" s="52"/>
       <c r="N186" s="52"/>
       <c r="O186" s="142" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="P186" s="143"/>
       <c r="Q186" s="143"/>
       <c r="R186" s="163"/>
       <c r="S186" s="154" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="T186" s="146"/>
       <c r="U186" s="147"/>
@@ -11608,13 +11457,13 @@
     </row>
     <row r="187" ht="13.05" customHeight="1" spans="1:31">
       <c r="A187" s="143" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="B187" s="156" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="C187" s="143" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D187" s="137"/>
       <c r="E187" s="135"/>
@@ -11624,10 +11473,10 @@
       </c>
       <c r="G187" s="91"/>
       <c r="H187" s="117" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="I187" s="158" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="J187" s="165"/>
       <c r="K187" s="141">
@@ -11635,7 +11484,7 @@
         <v>0</v>
       </c>
       <c r="L187" s="135" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="M187" s="135"/>
       <c r="N187" s="143"/>
@@ -11792,10 +11641,10 @@
     <row r="192" ht="13.05" customHeight="1" spans="1:31">
       <c r="A192" s="52"/>
       <c r="B192" s="156" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="C192" s="143" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D192" s="137"/>
       <c r="E192" s="135"/>
@@ -11805,10 +11654,10 @@
       </c>
       <c r="G192" s="91"/>
       <c r="H192" s="139" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="I192" s="140" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="J192" s="165"/>
       <c r="K192" s="141">
@@ -11970,13 +11819,13 @@
     </row>
     <row r="197" ht="13.05" customHeight="1" spans="1:31">
       <c r="A197" s="143" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="B197" s="156" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="C197" s="143" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D197" s="137"/>
       <c r="E197" s="135"/>
@@ -11986,10 +11835,10 @@
       </c>
       <c r="G197" s="91"/>
       <c r="H197" s="117" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="I197" s="158" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="J197" s="165"/>
       <c r="K197" s="141">
@@ -11997,7 +11846,7 @@
         <v>0</v>
       </c>
       <c r="L197" s="143" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="M197" s="135"/>
       <c r="N197" s="143"/>
@@ -12154,10 +12003,10 @@
     <row r="202" ht="13.05" customHeight="1" spans="1:31">
       <c r="A202" s="52"/>
       <c r="B202" s="156" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="C202" s="143" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D202" s="137"/>
       <c r="E202" s="143"/>
@@ -12167,10 +12016,10 @@
       </c>
       <c r="G202" s="91"/>
       <c r="H202" s="117" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="I202" s="158" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="J202" s="165"/>
       <c r="K202" s="147">
@@ -13145,7 +12994,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{52a087e9-77e8-40ad-89c3-410ec65a4af4}</x14:id>
+          <x14:id>{d7eee4cc-d652-44aa-97a0-0833074e5c96}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13157,7 +13006,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{84918bd0-b6cb-49bf-af7f-9253eda9f94c}</x14:id>
+          <x14:id>{c118b540-3bd5-4c84-9aa9-56545ba3944b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13169,7 +13018,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ac005b1c-66c3-4b24-ba1c-db5baca52e7c}</x14:id>
+          <x14:id>{64f37920-8032-433d-a88b-cd766d551e17}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13181,7 +13030,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{07a7593f-eacf-4125-824a-862ad7d1dd13}</x14:id>
+          <x14:id>{8f8474cf-7098-4d56-a18a-7a5e8fd240b5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13193,7 +13042,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0bbd6332-7652-4ec6-9da7-f3f29c61899b}</x14:id>
+          <x14:id>{71b5ac78-37f6-4d14-8ce8-b172f18a0b61}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13205,7 +13054,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{00e0dbc3-69ca-4919-8b9f-6edccd324a63}</x14:id>
+          <x14:id>{6d5c87ae-37fb-4a59-b5c0-25f5dc0acdad}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13217,7 +13066,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f1ecbad3-da7e-4e7b-bb84-37b97805ef44}</x14:id>
+          <x14:id>{05d656ff-126a-47ba-b63d-f3929f18aec1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13229,7 +13078,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f16bbfc6-317a-46d9-a5eb-99490e67592c}</x14:id>
+          <x14:id>{ec40a5eb-4e79-498e-960b-05d4a2d6bca4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13243,7 +13092,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{444ceffa-b5b2-49f8-9c77-77c343ec9e5b}</x14:id>
+          <x14:id>{83280b3c-36b3-4dbf-acc4-3075891329af}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13255,7 +13104,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4593b34d-9395-424e-bcb7-00151729fb58}</x14:id>
+          <x14:id>{17d29d50-6271-46f2-843e-5f417b20ea2e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13267,7 +13116,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3171dbec-962f-4f1d-b8de-2f109010a5e6}</x14:id>
+          <x14:id>{1e8fbbb6-5d45-4ba0-9d5e-f36ff26ad267}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13279,7 +13128,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4216d709-1760-4567-a9dd-6f94f91def5e}</x14:id>
+          <x14:id>{326b0244-cc8a-40f8-967a-a8fb4dc72f88}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13291,7 +13140,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{af842251-315f-4c7d-99c8-c95fad086953}</x14:id>
+          <x14:id>{607975c9-797e-4705-9e56-b17f240c31ab}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13303,7 +13152,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ea5c5103-43b8-48a7-a1c8-a8111ab4e863}</x14:id>
+          <x14:id>{d426b9af-7856-44b3-a807-828412b20ee5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13315,7 +13164,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{439bdc7a-663d-4cac-b5a9-8829d99e4455}</x14:id>
+          <x14:id>{5975584d-b102-40b7-850f-2b8ff50e8f66}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13327,7 +13176,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{06408ce4-5007-4bd9-bff3-97aa70e53a8e}</x14:id>
+          <x14:id>{fc0491ab-7ad9-4434-8c61-7dc5c9bf017e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13341,7 +13190,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{bc353f2f-1268-4a4a-bb86-380cba4aca7f}</x14:id>
+          <x14:id>{9d5902c9-c9bd-4a3e-b286-ff99bfb304b2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13353,7 +13202,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ae658228-ab93-4292-b2dd-7f74579068f2}</x14:id>
+          <x14:id>{e709284b-8493-4ff6-ab1b-0aa0288dd610}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13365,7 +13214,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{72dfe21b-638d-409a-a505-0f375fb06a8c}</x14:id>
+          <x14:id>{82df8c6a-2d6e-4a7a-96d1-5a5ed326b3d3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13377,7 +13226,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{71e5b8be-1e71-4521-9514-a89e2b0ceac1}</x14:id>
+          <x14:id>{1975b35b-2a82-44f4-baef-3fdd19dc3480}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13389,7 +13238,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3feb66af-a8be-43a2-84b0-1e2905bac6e0}</x14:id>
+          <x14:id>{67b17650-04b7-435e-8f57-8a3e391979f5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13401,7 +13250,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{68909a73-cd35-491b-b1e2-093bbc5226b9}</x14:id>
+          <x14:id>{b00d254d-d226-4d00-b930-bec5a9578842}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13413,7 +13262,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{bf80bcd4-e354-4800-b4a7-d07bba0299b5}</x14:id>
+          <x14:id>{74ee44f5-941e-4f70-86ab-db4fed61845b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13425,7 +13274,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{700b779f-e25d-4bd0-ba2e-afa37e3ef7d1}</x14:id>
+          <x14:id>{1a81d12f-d3e2-453e-829b-78c2d3f6100c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13439,7 +13288,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{dcb4d94e-f307-4126-9042-8c327d3fc773}</x14:id>
+          <x14:id>{510a3361-51e5-45d3-8adc-263adc9c0332}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13451,7 +13300,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a7d0f64e-df45-47d2-b2b1-80733a41fda3}</x14:id>
+          <x14:id>{da194053-84c9-4825-9a1c-c8ac2e6937c5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13463,7 +13312,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9138d6f7-0b17-42ba-8a86-595d1d286c50}</x14:id>
+          <x14:id>{ee4734d8-e7c8-4cf7-a361-45396c9817ee}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13475,7 +13324,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0c8fca9d-ae61-4223-889b-900b6b0eb462}</x14:id>
+          <x14:id>{9100a955-c92a-4f23-b11d-b86b9b9aef32}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13487,7 +13336,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c07c8c2c-4c02-4a3b-ba38-487d421381dd}</x14:id>
+          <x14:id>{371c02fa-b653-421b-b670-3240700b6b6d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13499,7 +13348,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9e22e885-5131-4536-91e7-ef42eea8685d}</x14:id>
+          <x14:id>{98beb0db-3856-4f9f-aa5b-341913471e36}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13511,7 +13360,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{da508674-c6b4-4e06-91d7-f203ae242417}</x14:id>
+          <x14:id>{a0322db3-c69b-4fc7-b774-0f390015695d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13523,7 +13372,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{dc8113c7-a83e-4c6e-b6a2-7d355352fda1}</x14:id>
+          <x14:id>{3108fbec-7598-427a-9b79-c69513103c50}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13537,7 +13386,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d6670f02-68ae-444a-8b33-71fbe1aa935e}</x14:id>
+          <x14:id>{b30327ca-b4b9-4da6-ab35-4fd493679ba3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13549,7 +13398,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{41709c5d-ccd3-4d75-9fad-1333f366a9bd}</x14:id>
+          <x14:id>{469f868b-afb3-4a78-ae24-72a7a993e34a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13561,7 +13410,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5a1e1e05-1b73-4d22-9ea4-e1b2a942336b}</x14:id>
+          <x14:id>{9ac7a6e1-f1ce-4f98-94eb-b61034aa83a3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13573,7 +13422,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3ba3147a-19cf-4533-bc3a-2f201838bbe5}</x14:id>
+          <x14:id>{5006eb6e-19cb-4b6f-b700-b7a21db131cc}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13585,7 +13434,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{da2be4d6-07a8-4384-b878-d375a880d479}</x14:id>
+          <x14:id>{e6dba9eb-a612-4999-b440-0025cefc7ec8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13597,7 +13446,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e609e0f7-3c6e-4bc2-b0d5-c1e2f6ce8acb}</x14:id>
+          <x14:id>{c606b7e2-f33d-4273-b5a7-8139cb1fe449}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13609,7 +13458,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f62c1fb3-99e2-42fd-85b6-16d2ec7f92b2}</x14:id>
+          <x14:id>{9f6a6f45-da95-438e-a094-36052905138a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13621,7 +13470,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0ee2e81f-ffc0-4b6b-b148-2d4369dc8ce9}</x14:id>
+          <x14:id>{3961a2bc-cc18-4727-b907-225a08653608}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13635,7 +13484,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{514a3a97-8c82-42c2-9cf9-25a22b2cfb04}</x14:id>
+          <x14:id>{69035e33-2029-41f6-9e25-a40d70cb594f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13647,7 +13496,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4108ae91-767d-4ad5-a953-0a400d8b9331}</x14:id>
+          <x14:id>{70778fea-b1a2-4221-bf77-634fb36daa44}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13659,7 +13508,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5811612b-ad6c-47e2-8079-be5dbdc327e2}</x14:id>
+          <x14:id>{8ad641ff-dc4f-4ea9-b874-ba7778544326}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13671,7 +13520,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{121e0d8d-2e56-4fd0-9401-2a4e670273e6}</x14:id>
+          <x14:id>{51253f83-acef-47c5-99fc-e8026332a34c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13683,7 +13532,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d74114de-6677-4f28-8810-07a22a4bb4e9}</x14:id>
+          <x14:id>{b414add0-7e91-4c18-b1e9-746b2b5b7b98}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13695,7 +13544,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b339f032-4497-4d48-b84f-adaf1b466f69}</x14:id>
+          <x14:id>{ec3c5a5e-44fe-4c1b-9309-349be2f47ff0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13707,7 +13556,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{921cf724-e1e6-40e7-8363-91a10a2d0e67}</x14:id>
+          <x14:id>{985b519a-8931-4e66-a205-6d9bc30e730e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13719,7 +13568,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{55e6e686-3bf1-41a2-a80f-b45dc1cce344}</x14:id>
+          <x14:id>{4885f2ed-fc08-4e4c-a7f3-c64204274de6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13733,7 +13582,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{087171f2-e4f4-4733-b8b3-054367bdbf45}</x14:id>
+          <x14:id>{85b784dd-b096-475b-94dd-f929a47ece06}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13745,7 +13594,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d9c959ca-abc4-431f-8e44-2f64dbb8ef24}</x14:id>
+          <x14:id>{4cd94ace-6f25-474c-aa3b-4f1d3496b049}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13757,7 +13606,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{90c0c043-e08b-4f58-928b-d32ea386eb03}</x14:id>
+          <x14:id>{7b33e90f-8866-4e19-8cb7-1ff291812372}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13769,7 +13618,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7fb41520-c38d-47b0-a2fb-ad8b1eef2c42}</x14:id>
+          <x14:id>{d55be3b2-0426-479d-9143-442f47e11b53}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13781,7 +13630,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d52d1d00-fb50-4d6c-a795-66295a540415}</x14:id>
+          <x14:id>{d55efaac-f121-42d8-aaa9-ab313046454a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13793,7 +13642,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fe64feb8-d2c1-4ac2-b8f5-e005985a8dd4}</x14:id>
+          <x14:id>{5b61a6eb-ab89-441f-bdce-80020d502133}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13805,7 +13654,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{958ce034-484d-49bb-a898-2bcd89cef20e}</x14:id>
+          <x14:id>{0ff1633b-60ae-4e54-ba02-bc0b09f847a6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13817,7 +13666,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9408be1f-3a0e-44b3-9ea5-f2108862315a}</x14:id>
+          <x14:id>{f13166eb-f93c-48b3-bbb6-7fc36e5bdab4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13831,7 +13680,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{95ee8ac1-2a32-4d3a-9d0f-2cf8439cf5e6}</x14:id>
+          <x14:id>{d1d227d4-9122-4a37-8c41-75939d02319c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13845,7 +13694,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fb44afd1-6156-43cc-919d-78925504e03c}</x14:id>
+          <x14:id>{c49f2160-af3e-480e-9c5e-25dc1f860371}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13859,7 +13708,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d2c92a7d-e043-4888-b626-081a75c7baba}</x14:id>
+          <x14:id>{80598930-406b-4e5a-bc2e-2021894ebb80}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13873,7 +13722,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6f8ad918-90b9-4ee0-a769-ea99521cc32f}</x14:id>
+          <x14:id>{b60a179d-d128-4b71-b429-282f6281b26e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13885,7 +13734,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d111187b-84a7-46d3-9a80-5d028d080b50}</x14:id>
+          <x14:id>{0497b6f5-5fa6-43be-b8cf-2424cb2fb637}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13897,7 +13746,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8cffef47-b03f-43fe-b409-3461f7c5e4e7}</x14:id>
+          <x14:id>{af957766-58e5-46d6-9388-f2ec597a330d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13909,7 +13758,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6e382d9f-658d-489a-9f5f-4a32fcc765a6}</x14:id>
+          <x14:id>{28d3386f-575b-48df-b99d-99efcb7214a0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13921,7 +13770,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0a9bffc7-4ebe-4062-b9c3-e564a2f15987}</x14:id>
+          <x14:id>{dc7592ee-e359-4fe3-b1b9-b56594d0db1b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13933,7 +13782,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{65979c97-e1a0-4e5a-b5ad-efc852661473}</x14:id>
+          <x14:id>{4dc3576b-86f0-4f7a-918f-9438c74c6e80}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13945,7 +13794,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9df2581d-dfe9-4ad2-8455-2970f059c385}</x14:id>
+          <x14:id>{47d55e57-d81e-4e9d-8b68-ff836a7f8920}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13957,7 +13806,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ba76ac0a-76b6-4dc1-90e2-24d536f9e706}</x14:id>
+          <x14:id>{86e5c3c3-4c5c-4671-94ac-0ebefbc41bac}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13971,7 +13820,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9b8e9dee-14e8-42ac-90f7-451b4fc1fcd4}</x14:id>
+          <x14:id>{da4ce47f-c0f3-4e62-bf67-b6a8607aaebf}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13983,7 +13832,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c28c05ff-f818-4a02-ad94-41076398aa4e}</x14:id>
+          <x14:id>{23db4c95-22c7-4d47-8855-512ccb2126b3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13997,7 +13846,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4346bffa-cbd1-4b39-9e89-6f2e05df5ad3}</x14:id>
+          <x14:id>{fbb361e7-3155-4e83-b5d2-233ac1ae43f9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14011,7 +13860,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0c6d02cc-3d74-4c79-8fd8-608688cca83e}</x14:id>
+          <x14:id>{0759b420-8d76-4e6d-9321-117cc29aed47}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14023,7 +13872,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ccb80669-820f-48f2-a2e3-3bb0e24b81e6}</x14:id>
+          <x14:id>{c2e391d2-17af-43d3-ac9e-5dcaa45227fb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14037,7 +13886,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5dd55e0f-6c2e-4f4f-a049-0524f706288f}</x14:id>
+          <x14:id>{339da861-ce7d-4a42-9549-e97b6a2b5418}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14049,7 +13898,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7263ba45-4c2a-4fe4-bcfa-30f0981da242}</x14:id>
+          <x14:id>{78967e01-25ef-4ac9-bbb7-54105b217b98}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14063,7 +13912,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e8ef2d72-5be9-43d8-a31a-4754ebf68687}</x14:id>
+          <x14:id>{396a10cc-2c96-40bd-afb2-3dd0ef03ef5d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14077,7 +13926,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{51c62212-470d-4633-8b5c-fb1b534f7f42}</x14:id>
+          <x14:id>{b00c9067-865f-425e-8937-cc682ee0fa35}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14089,7 +13938,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5e234413-352d-4f1f-91ae-2e9b14d8b1b7}</x14:id>
+          <x14:id>{7c0929a6-e809-4d5b-b0c0-645504750f56}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14103,7 +13952,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{71248b39-3d73-4616-a2be-488c161e872c}</x14:id>
+          <x14:id>{d69ef7a6-6287-4bbd-94da-7ff430d4b874}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14117,7 +13966,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fbbadaea-6eba-4cbf-9d47-1ab3c7819600}</x14:id>
+          <x14:id>{0f0df6c5-60b5-4aa7-806f-88392b35b341}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14129,7 +13978,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{68b414a3-3959-4bab-9bf2-c04a2ee75010}</x14:id>
+          <x14:id>{39d6e2d2-d02c-4641-9c11-c3e0bc5700d5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14141,7 +13990,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{235416d0-27ca-4f4c-bb3b-716e71231175}</x14:id>
+          <x14:id>{2361ebf2-8240-47f4-afaf-77449d369159}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14155,7 +14004,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{da6dfbf3-ccc8-442b-8f27-657e31d0b283}</x14:id>
+          <x14:id>{0d831924-d24d-4853-aeb3-df52b0eae0ef}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14167,7 +14016,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2894a6f6-0962-4ca9-9a38-1743751cf648}</x14:id>
+          <x14:id>{4b4d5b2b-b780-4e6c-aaef-d7e1fef554e0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14179,7 +14028,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{634ffc45-0ba2-4feb-9823-327ea9e7aa5e}</x14:id>
+          <x14:id>{a0dedd85-d717-484c-a1a6-7420c942e150}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14193,7 +14042,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{135ef8aa-c239-4ebf-9642-dece6b2e41db}</x14:id>
+          <x14:id>{7f796f19-504a-4b5a-b225-feb78c94589d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14205,21 +14054,19 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1319a2d8-df07-46e5-93cc-6ff18a4e271c}</x14:id>
+          <x14:id>{46e7d3b6-60a7-454a-ab8e-5be9a09e0612}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="8">
+  <dataValidations count="7">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:H2">
       <formula1>"白,夜"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:N2">
       <formula1>"晴,多云,小雨,大雨,阴,雾,霾"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5:F5 G16:G18 A11:B18 A20:B49 S15:T18">
-      <formula1>"A楼,B楼,C楼,D楼,E楼"</formula1>
-    </dataValidation>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5:F5 G7:O7 S7:AE7 G16:G18 S15:T18"/>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G5:H5">
       <formula1>"配电,弱电,暖通,消防,其他"</formula1>
     </dataValidation>
@@ -14229,11 +14076,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G6:I6 P6:R6">
       <formula1>"A班,B班,C班,D班"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G7:O7">
-      <formula1>" 刘治辉 刘恩山  伍喆 周海祥 曹大为,曹大为 刘丙全,/,汪建波 刘丙全 王庆华 周海祥,汪建波 王庆华 周海祥,汪建波 刘恩山 周海祥,汪建波 刘恩山 周海祥  王庆华, 刘恩山 周海祥  王庆华,王庆华"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S7:AE7">
-      <formula1>"   周海祥 刘治辉 刘恩山 伍喆  曹大为,汪建波 刘丙全 王庆华 周海祥,汪建波  王庆华 周海祥,汪建波  王庆华 ,汪建波  王庆华 伍喆,/, 王庆华 周海祥 刘恩山,王庆华 "</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A11:B18 A20:B49">
+      <formula1>"A楼,B楼,C楼,D楼,E楼"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -14247,7 +14091,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{52a087e9-77e8-40ad-89c3-410ec65a4af4}">
+          <x14:cfRule type="dataBar" id="{d7eee4cc-d652-44aa-97a0-0833074e5c96}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -14258,7 +14102,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{84918bd0-b6cb-49bf-af7f-9253eda9f94c}">
+          <x14:cfRule type="dataBar" id="{c118b540-3bd5-4c84-9aa9-56545ba3944b}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -14269,14 +14113,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{ac005b1c-66c3-4b24-ba1c-db5baca52e7c}">
+          <x14:cfRule type="dataBar" id="{64f37920-8032-433d-a88b-cd766d551e17}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{07a7593f-eacf-4125-824a-862ad7d1dd13}">
+          <x14:cfRule type="dataBar" id="{8f8474cf-7098-4d56-a18a-7a5e8fd240b5}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -14287,7 +14131,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{0bbd6332-7652-4ec6-9da7-f3f29c61899b}">
+          <x14:cfRule type="dataBar" id="{71b5ac78-37f6-4d14-8ce8-b172f18a0b61}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -14298,7 +14142,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{00e0dbc3-69ca-4919-8b9f-6edccd324a63}">
+          <x14:cfRule type="dataBar" id="{6d5c87ae-37fb-4a59-b5c0-25f5dc0acdad}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -14309,7 +14153,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{f1ecbad3-da7e-4e7b-bb84-37b97805ef44}">
+          <x14:cfRule type="dataBar" id="{05d656ff-126a-47ba-b63d-f3929f18aec1}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -14318,7 +14162,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{f16bbfc6-317a-46d9-a5eb-99490e67592c}">
+          <x14:cfRule type="dataBar" id="{ec40a5eb-4e79-498e-960b-05d4a2d6bca4}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -14330,7 +14174,7 @@
           <xm:sqref>AD56</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{444ceffa-b5b2-49f8-9c77-77c343ec9e5b}">
+          <x14:cfRule type="dataBar" id="{83280b3c-36b3-4dbf-acc4-3075891329af}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -14341,7 +14185,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{4593b34d-9395-424e-bcb7-00151729fb58}">
+          <x14:cfRule type="dataBar" id="{17d29d50-6271-46f2-843e-5f417b20ea2e}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -14352,14 +14196,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{3171dbec-962f-4f1d-b8de-2f109010a5e6}">
+          <x14:cfRule type="dataBar" id="{1e8fbbb6-5d45-4ba0-9d5e-f36ff26ad267}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{4216d709-1760-4567-a9dd-6f94f91def5e}">
+          <x14:cfRule type="dataBar" id="{326b0244-cc8a-40f8-967a-a8fb4dc72f88}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -14370,7 +14214,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{af842251-315f-4c7d-99c8-c95fad086953}">
+          <x14:cfRule type="dataBar" id="{607975c9-797e-4705-9e56-b17f240c31ab}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -14381,7 +14225,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{ea5c5103-43b8-48a7-a1c8-a8111ab4e863}">
+          <x14:cfRule type="dataBar" id="{d426b9af-7856-44b3-a807-828412b20ee5}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -14392,7 +14236,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{439bdc7a-663d-4cac-b5a9-8829d99e4455}">
+          <x14:cfRule type="dataBar" id="{5975584d-b102-40b7-850f-2b8ff50e8f66}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -14401,7 +14245,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{06408ce4-5007-4bd9-bff3-97aa70e53a8e}">
+          <x14:cfRule type="dataBar" id="{fc0491ab-7ad9-4434-8c61-7dc5c9bf017e}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -14413,7 +14257,7 @@
           <xm:sqref>K60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{bc353f2f-1268-4a4a-bb86-380cba4aca7f}">
+          <x14:cfRule type="dataBar" id="{9d5902c9-c9bd-4a3e-b286-ff99bfb304b2}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -14424,7 +14268,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{ae658228-ab93-4292-b2dd-7f74579068f2}">
+          <x14:cfRule type="dataBar" id="{e709284b-8493-4ff6-ab1b-0aa0288dd610}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -14435,14 +14279,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{72dfe21b-638d-409a-a505-0f375fb06a8c}">
+          <x14:cfRule type="dataBar" id="{82df8c6a-2d6e-4a7a-96d1-5a5ed326b3d3}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{71e5b8be-1e71-4521-9514-a89e2b0ceac1}">
+          <x14:cfRule type="dataBar" id="{1975b35b-2a82-44f4-baef-3fdd19dc3480}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -14453,7 +14297,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{3feb66af-a8be-43a2-84b0-1e2905bac6e0}">
+          <x14:cfRule type="dataBar" id="{67b17650-04b7-435e-8f57-8a3e391979f5}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -14464,7 +14308,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{68909a73-cd35-491b-b1e2-093bbc5226b9}">
+          <x14:cfRule type="dataBar" id="{b00d254d-d226-4d00-b930-bec5a9578842}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -14475,7 +14319,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{bf80bcd4-e354-4800-b4a7-d07bba0299b5}">
+          <x14:cfRule type="dataBar" id="{74ee44f5-941e-4f70-86ab-db4fed61845b}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -14484,7 +14328,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{700b779f-e25d-4bd0-ba2e-afa37e3ef7d1}">
+          <x14:cfRule type="dataBar" id="{1a81d12f-d3e2-453e-829b-78c2d3f6100c}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -14496,7 +14340,7 @@
           <xm:sqref>AD60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{dcb4d94e-f307-4126-9042-8c327d3fc773}">
+          <x14:cfRule type="dataBar" id="{510a3361-51e5-45d3-8adc-263adc9c0332}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -14507,7 +14351,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{a7d0f64e-df45-47d2-b2b1-80733a41fda3}">
+          <x14:cfRule type="dataBar" id="{da194053-84c9-4825-9a1c-c8ac2e6937c5}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -14518,14 +14362,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{9138d6f7-0b17-42ba-8a86-595d1d286c50}">
+          <x14:cfRule type="dataBar" id="{ee4734d8-e7c8-4cf7-a361-45396c9817ee}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{0c8fca9d-ae61-4223-889b-900b6b0eb462}">
+          <x14:cfRule type="dataBar" id="{9100a955-c92a-4f23-b11d-b86b9b9aef32}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -14536,7 +14380,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c07c8c2c-4c02-4a3b-ba38-487d421381dd}">
+          <x14:cfRule type="dataBar" id="{371c02fa-b653-421b-b670-3240700b6b6d}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -14547,7 +14391,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{9e22e885-5131-4536-91e7-ef42eea8685d}">
+          <x14:cfRule type="dataBar" id="{98beb0db-3856-4f9f-aa5b-341913471e36}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -14558,7 +14402,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{da508674-c6b4-4e06-91d7-f203ae242417}">
+          <x14:cfRule type="dataBar" id="{a0322db3-c69b-4fc7-b774-0f390015695d}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -14567,7 +14411,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{dc8113c7-a83e-4c6e-b6a2-7d355352fda1}">
+          <x14:cfRule type="dataBar" id="{3108fbec-7598-427a-9b79-c69513103c50}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -14579,7 +14423,7 @@
           <xm:sqref>K61</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d6670f02-68ae-444a-8b33-71fbe1aa935e}">
+          <x14:cfRule type="dataBar" id="{b30327ca-b4b9-4da6-ab35-4fd493679ba3}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -14590,7 +14434,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{41709c5d-ccd3-4d75-9fad-1333f366a9bd}">
+          <x14:cfRule type="dataBar" id="{469f868b-afb3-4a78-ae24-72a7a993e34a}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -14601,14 +14445,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{5a1e1e05-1b73-4d22-9ea4-e1b2a942336b}">
+          <x14:cfRule type="dataBar" id="{9ac7a6e1-f1ce-4f98-94eb-b61034aa83a3}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{3ba3147a-19cf-4533-bc3a-2f201838bbe5}">
+          <x14:cfRule type="dataBar" id="{5006eb6e-19cb-4b6f-b700-b7a21db131cc}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -14619,7 +14463,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{da2be4d6-07a8-4384-b878-d375a880d479}">
+          <x14:cfRule type="dataBar" id="{e6dba9eb-a612-4999-b440-0025cefc7ec8}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -14630,7 +14474,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e609e0f7-3c6e-4bc2-b0d5-c1e2f6ce8acb}">
+          <x14:cfRule type="dataBar" id="{c606b7e2-f33d-4273-b5a7-8139cb1fe449}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -14641,7 +14485,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{f62c1fb3-99e2-42fd-85b6-16d2ec7f92b2}">
+          <x14:cfRule type="dataBar" id="{9f6a6f45-da95-438e-a094-36052905138a}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -14650,7 +14494,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{0ee2e81f-ffc0-4b6b-b148-2d4369dc8ce9}">
+          <x14:cfRule type="dataBar" id="{3961a2bc-cc18-4727-b907-225a08653608}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -14662,7 +14506,7 @@
           <xm:sqref>K62</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{514a3a97-8c82-42c2-9cf9-25a22b2cfb04}">
+          <x14:cfRule type="dataBar" id="{69035e33-2029-41f6-9e25-a40d70cb594f}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -14673,7 +14517,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{4108ae91-767d-4ad5-a953-0a400d8b9331}">
+          <x14:cfRule type="dataBar" id="{70778fea-b1a2-4221-bf77-634fb36daa44}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -14684,14 +14528,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{5811612b-ad6c-47e2-8079-be5dbdc327e2}">
+          <x14:cfRule type="dataBar" id="{8ad641ff-dc4f-4ea9-b874-ba7778544326}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{121e0d8d-2e56-4fd0-9401-2a4e670273e6}">
+          <x14:cfRule type="dataBar" id="{51253f83-acef-47c5-99fc-e8026332a34c}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -14702,7 +14546,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{d74114de-6677-4f28-8810-07a22a4bb4e9}">
+          <x14:cfRule type="dataBar" id="{b414add0-7e91-4c18-b1e9-746b2b5b7b98}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -14713,7 +14557,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{b339f032-4497-4d48-b84f-adaf1b466f69}">
+          <x14:cfRule type="dataBar" id="{ec3c5a5e-44fe-4c1b-9309-349be2f47ff0}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -14724,7 +14568,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{921cf724-e1e6-40e7-8363-91a10a2d0e67}">
+          <x14:cfRule type="dataBar" id="{985b519a-8931-4e66-a205-6d9bc30e730e}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -14733,7 +14577,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{55e6e686-3bf1-41a2-a80f-b45dc1cce344}">
+          <x14:cfRule type="dataBar" id="{4885f2ed-fc08-4e4c-a7f3-c64204274de6}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -14745,7 +14589,7 @@
           <xm:sqref>K63</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{087171f2-e4f4-4733-b8b3-054367bdbf45}">
+          <x14:cfRule type="dataBar" id="{85b784dd-b096-475b-94dd-f929a47ece06}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -14756,7 +14600,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{d9c959ca-abc4-431f-8e44-2f64dbb8ef24}">
+          <x14:cfRule type="dataBar" id="{4cd94ace-6f25-474c-aa3b-4f1d3496b049}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -14767,14 +14611,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{90c0c043-e08b-4f58-928b-d32ea386eb03}">
+          <x14:cfRule type="dataBar" id="{7b33e90f-8866-4e19-8cb7-1ff291812372}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{7fb41520-c38d-47b0-a2fb-ad8b1eef2c42}">
+          <x14:cfRule type="dataBar" id="{d55be3b2-0426-479d-9143-442f47e11b53}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -14785,7 +14629,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{d52d1d00-fb50-4d6c-a795-66295a540415}">
+          <x14:cfRule type="dataBar" id="{d55efaac-f121-42d8-aaa9-ab313046454a}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -14796,7 +14640,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{fe64feb8-d2c1-4ac2-b8f5-e005985a8dd4}">
+          <x14:cfRule type="dataBar" id="{5b61a6eb-ab89-441f-bdce-80020d502133}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -14807,7 +14651,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{958ce034-484d-49bb-a898-2bcd89cef20e}">
+          <x14:cfRule type="dataBar" id="{0ff1633b-60ae-4e54-ba02-bc0b09f847a6}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -14816,7 +14660,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{9408be1f-3a0e-44b3-9ea5-f2108862315a}">
+          <x14:cfRule type="dataBar" id="{f13166eb-f93c-48b3-bbb6-7fc36e5bdab4}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -14828,7 +14672,7 @@
           <xm:sqref>K57:K58</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{95ee8ac1-2a32-4d3a-9d0f-2cf8439cf5e6}">
+          <x14:cfRule type="dataBar" id="{d1d227d4-9122-4a37-8c41-75939d02319c}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -14840,7 +14684,7 @@
           <xm:sqref>K187:K206</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{fb44afd1-6156-43cc-919d-78925504e03c}">
+          <x14:cfRule type="dataBar" id="{c49f2160-af3e-480e-9c5e-25dc1f860371}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -14852,7 +14696,7 @@
           <xm:sqref>AD56:AE57</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d2c92a7d-e043-4888-b626-081a75c7baba}">
+          <x14:cfRule type="dataBar" id="{80598930-406b-4e5a-bc2e-2021894ebb80}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -14864,7 +14708,7 @@
           <xm:sqref>AD60:AE63</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6f8ad918-90b9-4ee0-a769-ea99521cc32f}">
+          <x14:cfRule type="dataBar" id="{b60a179d-d128-4b71-b429-282f6281b26e}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -14875,7 +14719,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{d111187b-84a7-46d3-9a80-5d028d080b50}">
+          <x14:cfRule type="dataBar" id="{0497b6f5-5fa6-43be-b8cf-2424cb2fb637}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -14886,14 +14730,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{8cffef47-b03f-43fe-b409-3461f7c5e4e7}">
+          <x14:cfRule type="dataBar" id="{af957766-58e5-46d6-9388-f2ec597a330d}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{6e382d9f-658d-489a-9f5f-4a32fcc765a6}">
+          <x14:cfRule type="dataBar" id="{28d3386f-575b-48df-b99d-99efcb7214a0}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -14904,7 +14748,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{0a9bffc7-4ebe-4062-b9c3-e564a2f15987}">
+          <x14:cfRule type="dataBar" id="{dc7592ee-e359-4fe3-b1b9-b56594d0db1b}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -14915,7 +14759,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{65979c97-e1a0-4e5a-b5ad-efc852661473}">
+          <x14:cfRule type="dataBar" id="{4dc3576b-86f0-4f7a-918f-9438c74c6e80}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -14926,7 +14770,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{9df2581d-dfe9-4ad2-8455-2970f059c385}">
+          <x14:cfRule type="dataBar" id="{47d55e57-d81e-4e9d-8b68-ff836a7f8920}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -14935,7 +14779,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{ba76ac0a-76b6-4dc1-90e2-24d536f9e706}">
+          <x14:cfRule type="dataBar" id="{86e5c3c3-4c5c-4671-94ac-0ebefbc41bac}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -14947,7 +14791,7 @@
           <xm:sqref>F67 F77 F87 F97 F107 F117 F127 F137 F147 F157 F167 F177</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9b8e9dee-14e8-42ac-90f7-451b4fc1fcd4}">
+          <x14:cfRule type="dataBar" id="{da4ce47f-c0f3-4e62-bf67-b6a8607aaebf}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -14956,7 +14800,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c28c05ff-f818-4a02-ad94-41076398aa4e}">
+          <x14:cfRule type="dataBar" id="{23db4c95-22c7-4d47-8855-512ccb2126b3}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -14968,7 +14812,7 @@
           <xm:sqref>K67:K77 K83:K97 K103:K117 K123:K137 K143:K157 K163:K177 K183:K186</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4346bffa-cbd1-4b39-9e89-6f2e05df5ad3}">
+          <x14:cfRule type="dataBar" id="{fbb361e7-3155-4e83-b5d2-233ac1ae43f9}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -14980,7 +14824,7 @@
           <xm:sqref>Y67:Y77 Y83:Y97 Y103:Y120 Y123:Y139 Y143:Y158 Y163:Y177 Y183:Y186</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0c6d02cc-3d74-4c79-8fd8-608688cca83e}">
+          <x14:cfRule type="dataBar" id="{0759b420-8d76-4e6d-9321-117cc29aed47}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -14989,7 +14833,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{ccb80669-820f-48f2-a2e3-3bb0e24b81e6}">
+          <x14:cfRule type="dataBar" id="{c2e391d2-17af-43d3-ac9e-5dcaa45227fb}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15001,14 +14845,14 @@
           <xm:sqref>AB67 AB87 AB107 AB127 AB147 AB167</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5dd55e0f-6c2e-4f4f-a049-0524f706288f}">
+          <x14:cfRule type="dataBar" id="{339da861-ce7d-4a42-9549-e97b6a2b5418}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{7263ba45-4c2a-4fe4-bcfa-30f0981da242}">
+          <x14:cfRule type="dataBar" id="{78967e01-25ef-4ac9-bbb7-54105b217b98}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15020,7 +14864,7 @@
           <xm:sqref>AB67:AB77 AB83:AB97 AB103:AB120 AB123:AB139 AB143:AB158 AB163:AB177 AB183:AB186</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e8ef2d72-5be9-43d8-a31a-4754ebf68687}">
+          <x14:cfRule type="dataBar" id="{396a10cc-2c96-40bd-afb2-3dd0ef03ef5d}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15032,7 +14876,7 @@
           <xm:sqref>AB67:AB77 AB83:AB97 AB103:AB117 AB123:AB137 AB143:AB157 AB163:AB177 AB183:AB186</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{51c62212-470d-4633-8b5c-fb1b534f7f42}">
+          <x14:cfRule type="dataBar" id="{b00c9067-865f-425e-8937-cc682ee0fa35}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15041,7 +14885,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{5e234413-352d-4f1f-91ae-2e9b14d8b1b7}">
+          <x14:cfRule type="dataBar" id="{7c0929a6-e809-4d5b-b0c0-645504750f56}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15053,7 +14897,7 @@
           <xm:sqref>K78:K82 K98:K102 K118:K122 K138:K142 K158:K162 K178:K182</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{71248b39-3d73-4616-a2be-488c161e872c}">
+          <x14:cfRule type="dataBar" id="{d69ef7a6-6287-4bbd-94da-7ff430d4b874}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15065,14 +14909,14 @@
           <xm:sqref>Y78:Y82 Y98:Y102 Y118:Y122 Y138:Y142 Y158:Y162 Y178:Y182</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{fbbadaea-6eba-4cbf-9d47-1ab3c7819600}">
+          <x14:cfRule type="dataBar" id="{0f0df6c5-60b5-4aa7-806f-88392b35b341}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{68b414a3-3959-4bab-9bf2-c04a2ee75010}">
+          <x14:cfRule type="dataBar" id="{39d6e2d2-d02c-4641-9c11-c3e0bc5700d5}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15081,7 +14925,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{235416d0-27ca-4f4c-bb3b-716e71231175}">
+          <x14:cfRule type="dataBar" id="{2361ebf2-8240-47f4-afaf-77449d369159}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15093,7 +14937,7 @@
           <xm:sqref>AB78:AB82 AB98:AB102 AB118:AB122 AB138:AB142 AB158:AB162 AB178:AB182</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{da6dfbf3-ccc8-442b-8f27-657e31d0b283}">
+          <x14:cfRule type="dataBar" id="{0d831924-d24d-4853-aeb3-df52b0eae0ef}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15102,7 +14946,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{2894a6f6-0962-4ca9-9a38-1743751cf648}">
+          <x14:cfRule type="dataBar" id="{4b4d5b2b-b780-4e6c-aaef-d7e1fef554e0}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15111,7 +14955,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{634ffc45-0ba2-4feb-9823-327ea9e7aa5e}">
+          <x14:cfRule type="dataBar" id="{a0dedd85-d717-484c-a1a6-7420c942e150}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15123,7 +14967,7 @@
           <xm:sqref>F187 F192 F197 F202</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{135ef8aa-c239-4ebf-9642-dece6b2e41db}">
+          <x14:cfRule type="dataBar" id="{7f796f19-504a-4b5a-b225-feb78c94589d}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15132,7 +14976,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{1319a2d8-df07-46e5-93cc-6ff18a4e271c}">
+          <x14:cfRule type="dataBar" id="{46e7d3b6-60a7-454a-ab8e-5be9a09e0612}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15163,63 +15007,63 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>472</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>474</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>476</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>477</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>478</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>479</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>480</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>483</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="R1" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="Q1" s="3" t="s">
-        <v>488</v>
-      </c>
-      <c r="R1" s="3" t="s">
-        <v>489</v>
       </c>
     </row>
     <row r="2" spans="1:18">
       <c r="A2" s="3" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="B2" s="4">
         <v>36.11</v>
@@ -15273,7 +15117,7 @@
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="3" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="B3" s="6">
         <v>12689.5</v>
@@ -15330,7 +15174,7 @@
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:18">
       <c r="A4" s="9" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="B4" s="7">
         <f t="shared" ref="B4:O4" si="0">B3*0.86/1000</f>
@@ -15401,7 +15245,7 @@
     </row>
     <row r="6" spans="1:18">
       <c r="A6" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
     </row>
   </sheetData>
